--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,252 +396,252 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2">
-        <v>128</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>390</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>84</v>
+        <v>159</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>93</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>145</v>
+        <v>201</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>167</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>159</v>
+        <v>361</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>806</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>225</v>
+        <v>434</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>335</v>
+        <v>523</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>1451</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>345</v>
+        <v>583</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>349</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>434</v>
+        <v>990</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>110</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>440</v>
+        <v>1124</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>225</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>515</v>
+        <v>1309</v>
       </c>
       <c r="B12">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>239</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>624</v>
+        <v>1413</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>116</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>955</v>
+        <v>1504</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14">
-        <v>116</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>972</v>
+        <v>1654</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>666</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>995</v>
+        <v>1801</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>1309</v>
+        <v>2055</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>60</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>1407</v>
+        <v>2105</v>
       </c>
       <c r="B18">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>106</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1446</v>
+        <v>2328</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>148</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1504</v>
+        <v>2423</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>1598</v>
+        <v>2424</v>
       </c>
       <c r="B21">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>1599</v>
+        <v>2774</v>
       </c>
       <c r="B22">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1703</v>
+        <v>2778</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>179</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>1801</v>
+        <v>3334</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>7</v>
@@ -649,252 +649,252 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>2105</v>
+        <v>3462</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>323</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>2188</v>
+        <v>3495</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C26">
-        <v>78</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>2331</v>
+        <v>3674</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>2423</v>
+        <v>5151</v>
       </c>
       <c r="B28">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>212</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>2424</v>
+        <v>5165</v>
       </c>
       <c r="B29">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>191</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>2774</v>
+        <v>5584</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>198</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>2912</v>
+        <v>5585</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>55</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>3610</v>
+        <v>7558</v>
       </c>
       <c r="B32">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>233</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>3840</v>
+        <v>7567</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>191</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>5005</v>
+        <v>8753</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>5153</v>
+        <v>8915</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35">
-        <v>27</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>5491</v>
+        <v>10993</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36">
-        <v>113</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>5538</v>
+        <v>11467</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>5539</v>
+        <v>11504</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>5541</v>
+        <v>11681</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>8</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>5660</v>
+        <v>11814</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>221</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>5812</v>
+        <v>11855</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>675</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>6158</v>
+        <v>12791</v>
       </c>
       <c r="B42">
         <v>2</v>
       </c>
       <c r="C42">
-        <v>296</v>
+        <v>344</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>6540</v>
+        <v>12924</v>
       </c>
       <c r="B43">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>85</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>6935</v>
+        <v>19685</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>7084</v>
+        <v>21686</v>
       </c>
       <c r="B45">
         <v>3</v>
       </c>
       <c r="C45">
-        <v>144</v>
+        <v>853</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>8106</v>
+        <v>21793</v>
       </c>
       <c r="B46">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>78</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>8157</v>
+        <v>23380</v>
       </c>
       <c r="B47">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="C47">
         <v>7</v>
@@ -902,299 +902,24 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>8356</v>
+        <v>24724</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48">
-        <v>99</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>8754</v>
+        <v>25899</v>
       </c>
       <c r="B49">
         <v>2</v>
       </c>
       <c r="C49">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50">
-        <v>8915</v>
-      </c>
-      <c r="B50">
-        <v>2</v>
-      </c>
-      <c r="C50">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51">
-        <v>9182</v>
-      </c>
-      <c r="B51">
-        <v>1</v>
-      </c>
-      <c r="C51">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52">
-        <v>9358</v>
-      </c>
-      <c r="B52">
-        <v>1</v>
-      </c>
-      <c r="C52">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53">
-        <v>9760</v>
-      </c>
-      <c r="B53">
-        <v>29</v>
-      </c>
-      <c r="C53">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54">
-        <v>11039</v>
-      </c>
-      <c r="B54">
-        <v>2</v>
-      </c>
-      <c r="C54">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55">
-        <v>11226</v>
-      </c>
-      <c r="B55">
-        <v>1</v>
-      </c>
-      <c r="C55">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56">
-        <v>11396</v>
-      </c>
-      <c r="B56">
-        <v>2</v>
-      </c>
-      <c r="C56">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57">
-        <v>11467</v>
-      </c>
-      <c r="B57">
-        <v>1</v>
-      </c>
-      <c r="C57">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58">
-        <v>11504</v>
-      </c>
-      <c r="B58">
-        <v>2</v>
-      </c>
-      <c r="C58">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59">
-        <v>11582</v>
-      </c>
-      <c r="B59">
-        <v>29</v>
-      </c>
-      <c r="C59">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60">
-        <v>11844</v>
-      </c>
-      <c r="B60">
-        <v>2</v>
-      </c>
-      <c r="C60">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61">
-        <v>11855</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
-      </c>
-      <c r="C61">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62">
-        <v>11887</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
-      </c>
-      <c r="C62">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63">
-        <v>11895</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
-      </c>
-      <c r="C63">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64">
-        <v>12304</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
-      </c>
-      <c r="C64">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65">
-        <v>12536</v>
-      </c>
-      <c r="B65">
-        <v>2</v>
-      </c>
-      <c r="C65">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66">
-        <v>12538</v>
-      </c>
-      <c r="B66">
-        <v>3</v>
-      </c>
-      <c r="C66">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67">
-        <v>13114</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
-      </c>
-      <c r="C67">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68">
-        <v>20555</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
-      <c r="C68">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69">
-        <v>21793</v>
-      </c>
-      <c r="B69">
-        <v>1</v>
-      </c>
-      <c r="C69">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70">
-        <v>24252</v>
-      </c>
-      <c r="B70">
-        <v>1</v>
-      </c>
-      <c r="C70">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71">
-        <v>24253</v>
-      </c>
-      <c r="B71">
-        <v>1</v>
-      </c>
-      <c r="C71">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72">
-        <v>24566</v>
-      </c>
-      <c r="B72">
-        <v>1</v>
-      </c>
-      <c r="C72">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73">
-        <v>24707</v>
-      </c>
-      <c r="B73">
-        <v>3</v>
-      </c>
-      <c r="C73">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74">
-        <v>24724</v>
-      </c>
-      <c r="B74">
-        <v>2</v>
-      </c>
-      <c r="C74">
-        <v>68</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,81 +402,81 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>66</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>84</v>
+        <v>206</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8">
-        <v>930</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>114</v>
+        <v>215</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -484,527 +484,527 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>140</v>
+        <v>216</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>142</v>
+        <v>307</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11">
-        <v>65</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>159</v>
+        <v>358</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>205</v>
+        <v>361</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>215</v>
+        <v>378</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>225</v>
+        <v>413</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>248</v>
+        <v>417</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>22</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>307</v>
+        <v>474</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>84</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>358</v>
+        <v>590</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>378</v>
+        <v>593</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>154</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>413</v>
+        <v>615</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>417</v>
+        <v>616</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>70</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>434</v>
+        <v>823</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>474</v>
+        <v>950</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>583</v>
+        <v>955</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>589</v>
+        <v>990</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>590</v>
+        <v>1012</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>616</v>
+        <v>1124</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>42</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>950</v>
+        <v>1126</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>24</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>955</v>
+        <v>1429</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29">
-        <v>47</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>990</v>
+        <v>1432</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C30">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1012</v>
+        <v>1490</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1124</v>
+        <v>1492</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>79</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1126</v>
+        <v>1504</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33">
-        <v>95</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1446</v>
+        <v>1598</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C34">
-        <v>73</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1492</v>
+        <v>1601</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C35">
-        <v>16</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1504</v>
+        <v>1602</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C36">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1598</v>
+        <v>1654</v>
       </c>
       <c r="B37">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>148</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1601</v>
+        <v>1801</v>
       </c>
       <c r="B38">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>82</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1602</v>
+        <v>2057</v>
       </c>
       <c r="B39">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>201</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1801</v>
+        <v>2105</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>42</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2105</v>
+        <v>2161</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>163</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2109</v>
+        <v>2234</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2161</v>
+        <v>2328</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>19</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2234</v>
+        <v>2331</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2328</v>
+        <v>2423</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C45">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2331</v>
+        <v>2424</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C46">
-        <v>50</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2423</v>
+        <v>2508</v>
       </c>
       <c r="B47">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2424</v>
+        <v>2735</v>
       </c>
       <c r="B48">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>72</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2497</v>
+        <v>2736</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2508</v>
+        <v>2912</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2735</v>
+        <v>2934</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2736</v>
+        <v>3451</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2774</v>
+        <v>3495</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>12</v>
+        <v>459</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2776</v>
+        <v>3576</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C54">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2778</v>
+        <v>3671</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2934</v>
+        <v>3892</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3451</v>
+        <v>3898</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57">
         <v>7</v>
@@ -1012,54 +1012,54 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3495</v>
+        <v>3899</v>
       </c>
       <c r="B58">
         <v>3</v>
       </c>
       <c r="C58">
-        <v>455</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3670</v>
+        <v>3909</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C59">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3674</v>
+        <v>4043</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C60">
-        <v>101</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3892</v>
+        <v>4867</v>
       </c>
       <c r="B61">
         <v>1</v>
       </c>
       <c r="C61">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3898</v>
+        <v>5152</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62">
         <v>7</v>
@@ -1067,233 +1067,233 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3899</v>
+        <v>5153</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>3909</v>
+        <v>5165</v>
       </c>
       <c r="B64">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>298</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>4867</v>
+        <v>5491</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5151</v>
+        <v>5493</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5152</v>
+        <v>5538</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5153</v>
+        <v>5539</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5491</v>
+        <v>5541</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5493</v>
+        <v>5577</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>43</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5538</v>
+        <v>5585</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C71">
-        <v>73</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5539</v>
+        <v>5642</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5541</v>
+        <v>5660</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5577</v>
+        <v>6097</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C74">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5585</v>
+        <v>6158</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5642</v>
+        <v>6494</v>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>5660</v>
+        <v>6496</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>83</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6098</v>
+        <v>6497</v>
       </c>
       <c r="B78">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6158</v>
+        <v>6540</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C79">
-        <v>112</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>6540</v>
+        <v>6575</v>
       </c>
       <c r="B80">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>33</v>
+        <v>112</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>6575</v>
+        <v>6872</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C81">
-        <v>110</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>6952</v>
+        <v>6965</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C82">
-        <v>157</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>6965</v>
+        <v>7005</v>
       </c>
       <c r="B83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1315,260 +1315,260 @@
         <v>3</v>
       </c>
       <c r="C85">
-        <v>98</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>7558</v>
+        <v>7567</v>
       </c>
       <c r="B86">
         <v>3</v>
       </c>
       <c r="C86">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>7567</v>
+        <v>7885</v>
       </c>
       <c r="B87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>7885</v>
+        <v>7886</v>
       </c>
       <c r="B88">
         <v>4</v>
       </c>
       <c r="C88">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>7886</v>
+        <v>7887</v>
       </c>
       <c r="B89">
         <v>4</v>
       </c>
       <c r="C89">
-        <v>60</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>7887</v>
+        <v>8089</v>
       </c>
       <c r="B90">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>59</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8089</v>
+        <v>8356</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8216</v>
+        <v>8907</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C92">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8356</v>
+        <v>8915</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>36</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8648</v>
+        <v>8926</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>154</v>
+        <v>27</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>8649</v>
+        <v>8938</v>
       </c>
       <c r="B95">
         <v>2</v>
       </c>
       <c r="C95">
-        <v>128</v>
+        <v>69</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>8650</v>
+        <v>9070</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>77</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>8753</v>
+        <v>9182</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>147</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>8754</v>
+        <v>9358</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>148</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>8938</v>
+        <v>9531</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C99">
-        <v>69</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9070</v>
+        <v>9760</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C100">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>9182</v>
+        <v>10507</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>9358</v>
+        <v>10517</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>9531</v>
+        <v>10716</v>
       </c>
       <c r="B103">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10507</v>
+        <v>10717</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C104">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10716</v>
+        <v>10721</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C105">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>10717</v>
+        <v>10993</v>
       </c>
       <c r="B106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>10993</v>
+        <v>11039</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107">
-        <v>23</v>
+        <v>135</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11090</v>
+        <v>11150</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>7</v>
+        <v>149</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -1584,24 +1584,24 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11306</v>
+        <v>11402</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11402</v>
+        <v>11403</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -1617,57 +1617,57 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11681</v>
+        <v>11492</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>113</v>
+        <v>39</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11685</v>
+        <v>11583</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C114">
-        <v>111</v>
+        <v>31</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11738</v>
+        <v>11684</v>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115">
-        <v>26</v>
+        <v>188</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11739</v>
+        <v>11738</v>
       </c>
       <c r="B116">
         <v>2</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11772</v>
+        <v>11739</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>90</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -1678,7 +1678,7 @@
         <v>2</v>
       </c>
       <c r="C118">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -1700,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="C120">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -1755,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="C125">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -1821,29 +1821,29 @@
         <v>2</v>
       </c>
       <c r="C131">
-        <v>319</v>
+        <v>307</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>12923</v>
+        <v>12791</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C132">
-        <v>16</v>
+        <v>349</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>12924</v>
+        <v>12923</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -1903,73 +1903,73 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>19925</v>
+        <v>13965</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C139">
-        <v>128</v>
+        <v>43</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>19996</v>
+        <v>13968</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>24</v>
+        <v>85</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>20223</v>
+        <v>19685</v>
       </c>
       <c r="B141">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>20555</v>
+        <v>19996</v>
       </c>
       <c r="B142">
         <v>2</v>
       </c>
       <c r="C142">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>20927</v>
+        <v>20223</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C143">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>21454</v>
+        <v>20555</v>
       </c>
       <c r="B144">
         <v>2</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>22665</v>
+        <v>21454</v>
       </c>
       <c r="B145">
         <v>2</v>
@@ -1980,21 +1980,21 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>23262</v>
+        <v>21793</v>
       </c>
       <c r="B146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>7</v>
+        <v>101</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>24252</v>
+        <v>22665</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C147">
         <v>7</v>
@@ -2002,35 +2002,57 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>24253</v>
+        <v>23262</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C148">
-        <v>81</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>24724</v>
+        <v>24252</v>
       </c>
       <c r="B149">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C149">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
+        <v>24253</v>
+      </c>
+      <c r="B150">
+        <v>1</v>
+      </c>
+      <c r="C150">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>24724</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
         <v>25899</v>
       </c>
-      <c r="B150">
-        <v>2</v>
-      </c>
-      <c r="C150">
-        <v>130</v>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C151"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,7 +402,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -413,125 +413,125 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4">
-        <v>151</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>640</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>65</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>65</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>206</v>
+        <v>145</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14">
         <v>7</v>
@@ -539,32 +539,32 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>305</v>
+        <v>206</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15">
-        <v>62</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>307</v>
+        <v>215</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C16">
-        <v>84</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -572,46 +572,46 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>361</v>
+        <v>248</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>65</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>362</v>
+        <v>305</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>378</v>
+        <v>307</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>102</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>42</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -622,7 +622,7 @@
         <v>1</v>
       </c>
       <c r="C22">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -633,48 +633,48 @@
         <v>1</v>
       </c>
       <c r="C23">
-        <v>35</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>470</v>
+        <v>417</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>474</v>
+        <v>523</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>515</v>
+        <v>615</v>
       </c>
       <c r="B26">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>91</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>590</v>
+        <v>616</v>
       </c>
       <c r="B27">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <v>43</v>
@@ -682,7 +682,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -732,51 +732,51 @@
         <v>2</v>
       </c>
       <c r="C32">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1432</v>
+        <v>1126</v>
       </c>
       <c r="B33">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>40</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1490</v>
+        <v>1432</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C34">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1504</v>
+        <v>1492</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>73</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -798,7 +798,7 @@
         <v>68</v>
       </c>
       <c r="C38">
-        <v>185</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -814,274 +814,274 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2057</v>
+        <v>1654</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>200</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2161</v>
+        <v>1656</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2234</v>
+        <v>1700</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2328</v>
+        <v>2161</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>110</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2331</v>
+        <v>2234</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44">
-        <v>53</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2423</v>
+        <v>2328</v>
       </c>
       <c r="B45">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>82</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2424</v>
+        <v>2331</v>
       </c>
       <c r="B46">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>74</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2508</v>
+        <v>2423</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2735</v>
+        <v>2424</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C48">
-        <v>23</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2736</v>
+        <v>2497</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>23</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2912</v>
+        <v>2508</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2934</v>
+        <v>2735</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3495</v>
+        <v>2774</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>468</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3576</v>
+        <v>2776</v>
       </c>
       <c r="B53">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3577</v>
+        <v>2912</v>
       </c>
       <c r="B54">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3891</v>
+        <v>2934</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55">
-        <v>80</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3892</v>
+        <v>3451</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>80</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3893</v>
+        <v>3495</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57">
-        <v>47</v>
+        <v>468</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3898</v>
+        <v>3577</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3899</v>
+        <v>3674</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>16</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3909</v>
+        <v>3889</v>
       </c>
       <c r="B60">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>128</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4586</v>
+        <v>3891</v>
       </c>
       <c r="B61">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>607</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>4867</v>
+        <v>3892</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5005</v>
+        <v>3893</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5152</v>
+        <v>3898</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64">
         <v>7</v>
@@ -1089,32 +1089,32 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5153</v>
+        <v>3899</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5491</v>
+        <v>4867</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5538</v>
+        <v>5152</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67">
         <v>7</v>
@@ -1122,178 +1122,178 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5539</v>
+        <v>5153</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5541</v>
+        <v>5164</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5577</v>
+        <v>5538</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5585</v>
+        <v>5539</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5642</v>
+        <v>5541</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5660</v>
+        <v>5577</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>6097</v>
+        <v>5585</v>
       </c>
       <c r="B74">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>39</v>
+        <v>111</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6158</v>
+        <v>5642</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>112</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6494</v>
+        <v>5660</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6496</v>
+        <v>6158</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>17</v>
+        <v>329</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6497</v>
+        <v>6494</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6540</v>
+        <v>6496</v>
       </c>
       <c r="B79">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>6575</v>
+        <v>6497</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>114</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>6872</v>
+        <v>6540</v>
       </c>
       <c r="B81">
         <v>25</v>
       </c>
       <c r="C81">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>6965</v>
+        <v>6935</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82">
-        <v>7</v>
+        <v>231</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>7084</v>
+        <v>7005</v>
       </c>
       <c r="B83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>108</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1309,351 +1309,351 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>7885</v>
+        <v>7558</v>
       </c>
       <c r="B85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C85">
-        <v>59</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>7886</v>
+        <v>7567</v>
       </c>
       <c r="B86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C86">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8356</v>
+        <v>7885</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C87">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8907</v>
+        <v>7886</v>
       </c>
       <c r="B88">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8926</v>
+        <v>8356</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9070</v>
+        <v>8648</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>15</v>
+        <v>153</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9208</v>
+        <v>8649</v>
       </c>
       <c r="B91">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>42</v>
+        <v>77</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9209</v>
+        <v>8650</v>
       </c>
       <c r="B92">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>9239</v>
+        <v>8915</v>
       </c>
       <c r="B93">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>12</v>
+        <v>67</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9358</v>
+        <v>8938</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9507</v>
+        <v>9208</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C95">
-        <v>253</v>
+        <v>42</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9531</v>
+        <v>9209</v>
       </c>
       <c r="B96">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C96">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10507</v>
+        <v>9239</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C97">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10517</v>
+        <v>9396</v>
       </c>
       <c r="B98">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10716</v>
+        <v>9910</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C99">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10717</v>
+        <v>10716</v>
       </c>
       <c r="B100">
         <v>3</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10993</v>
+        <v>10717</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C101">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11089</v>
+        <v>10719</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C102">
-        <v>95</v>
+        <v>42</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11226</v>
+        <v>10720</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11396</v>
+        <v>10721</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C104">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11402</v>
+        <v>10993</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11403</v>
+        <v>11150</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11492</v>
+        <v>11306</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11684</v>
+        <v>11396</v>
       </c>
       <c r="B108">
         <v>2</v>
       </c>
       <c r="C108">
-        <v>113</v>
+        <v>39</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11685</v>
+        <v>11402</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>188</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11737</v>
+        <v>11403</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11738</v>
+        <v>11426</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11739</v>
+        <v>11492</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11844</v>
+        <v>11684</v>
       </c>
       <c r="B113">
         <v>2</v>
       </c>
       <c r="C113">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11895</v>
+        <v>11685</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>188</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11965</v>
+        <v>11738</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12045</v>
+        <v>11739</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116">
         <v>7</v>
@@ -1661,18 +1661,18 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12050</v>
+        <v>11952</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117">
-        <v>7</v>
+        <v>245</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12128</v>
+        <v>12050</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12340</v>
+        <v>12128</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12597</v>
+        <v>12612</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -1749,40 +1749,40 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12612</v>
+        <v>12791</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>348</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12764</v>
+        <v>12923</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>307</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12925</v>
+        <v>12924</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13114</v>
+        <v>12925</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13115</v>
+        <v>13114</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -1854,7 +1854,7 @@
         <v>29</v>
       </c>
       <c r="C134">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13272</v>
+        <v>13968</v>
       </c>
       <c r="B137">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C137">
         <v>43</v>
@@ -1892,43 +1892,43 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>13962</v>
+        <v>20927</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>13968</v>
+        <v>21454</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C139">
-        <v>85</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>19996</v>
+        <v>21793</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>24</v>
+        <v>306</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>20223</v>
+        <v>22665</v>
       </c>
       <c r="B141">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C141">
         <v>7</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>20555</v>
+        <v>23235</v>
       </c>
       <c r="B142">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C142">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>20927</v>
+        <v>23262</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C143">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>21454</v>
+        <v>24252</v>
       </c>
       <c r="B144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C144">
         <v>7</v>
@@ -1969,29 +1969,29 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>21793</v>
+        <v>24253</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>306</v>
+        <v>81</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>22665</v>
+        <v>24257</v>
       </c>
       <c r="B146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23262</v>
+        <v>24724</v>
       </c>
       <c r="B147">
         <v>2</v>
@@ -2002,45 +2002,12 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>24252</v>
+        <v>25899</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C148">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149">
-        <v>24253</v>
-      </c>
-      <c r="B149">
-        <v>1</v>
-      </c>
-      <c r="C149">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150">
-        <v>24724</v>
-      </c>
-      <c r="B150">
-        <v>2</v>
-      </c>
-      <c r="C150">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151">
-        <v>25899</v>
-      </c>
-      <c r="B151">
-        <v>2</v>
-      </c>
-      <c r="C151">
         <v>37</v>
       </c>
     </row>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,7 +402,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -424,7 +424,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>92</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -451,637 +451,637 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>65</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>144</v>
+        <v>214</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>65</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>66</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>159</v>
+        <v>216</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13">
-        <v>301</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>206</v>
+        <v>358</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>215</v>
+        <v>378</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>17</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>216</v>
+        <v>385</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>248</v>
+        <v>470</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>305</v>
+        <v>593</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>63</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>307</v>
+        <v>624</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>84</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>378</v>
+        <v>823</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>102</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>412</v>
+        <v>955</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>416</v>
+        <v>957</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>72</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>417</v>
+        <v>991</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>523</v>
+        <v>997</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>85</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>615</v>
+        <v>998</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>616</v>
+        <v>1012</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>624</v>
+        <v>1126</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28">
-        <v>44</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>823</v>
+        <v>1432</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C29">
-        <v>17</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>957</v>
+        <v>1490</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>990</v>
+        <v>1492</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1012</v>
+        <v>1598</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1126</v>
+        <v>1601</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C33">
-        <v>97</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1432</v>
+        <v>1602</v>
       </c>
       <c r="B34">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="C34">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1490</v>
+        <v>1654</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1492</v>
+        <v>1656</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>16</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1598</v>
+        <v>1700</v>
       </c>
       <c r="B37">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>148</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1601</v>
+        <v>2161</v>
       </c>
       <c r="B38">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1602</v>
+        <v>2234</v>
       </c>
       <c r="B39">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1654</v>
+        <v>2328</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40">
-        <v>38</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1656</v>
+        <v>2331</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>1700</v>
+        <v>2423</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C42">
-        <v>40</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2161</v>
+        <v>2424</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C43">
-        <v>20</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2234</v>
+        <v>2497</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>14</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2328</v>
+        <v>2508</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45">
-        <v>110</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2331</v>
+        <v>2735</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>51</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2423</v>
+        <v>2736</v>
       </c>
       <c r="B47">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>82</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2424</v>
+        <v>2774</v>
       </c>
       <c r="B48">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C48">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2497</v>
+        <v>2912</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2508</v>
+        <v>2934</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2735</v>
+        <v>3451</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2774</v>
+        <v>3495</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>77</v>
+        <v>468</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2776</v>
+        <v>3577</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C53">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2912</v>
+        <v>3670</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>21</v>
+        <v>222</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2934</v>
+        <v>3674</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>12</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3451</v>
+        <v>3889</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3495</v>
+        <v>3891</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>468</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3577</v>
+        <v>3892</v>
       </c>
       <c r="B58">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>37</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3674</v>
+        <v>3893</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3889</v>
+        <v>3898</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C60">
-        <v>64</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3891</v>
+        <v>3899</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>64</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3892</v>
+        <v>3909</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C62">
-        <v>80</v>
+        <v>295</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3893</v>
+        <v>4586</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C63">
-        <v>96</v>
+        <v>614</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>3898</v>
+        <v>4867</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64">
         <v>7</v>
@@ -1089,365 +1089,365 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>3899</v>
+        <v>5152</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>4867</v>
+        <v>5153</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5152</v>
+        <v>5165</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5153</v>
+        <v>5538</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5164</v>
+        <v>5539</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5538</v>
+        <v>5541</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5539</v>
+        <v>5577</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C71">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5541</v>
+        <v>5585</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5577</v>
+        <v>5642</v>
       </c>
       <c r="B73">
         <v>3</v>
       </c>
       <c r="C73">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5585</v>
+        <v>5660</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>111</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5642</v>
+        <v>6158</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5660</v>
+        <v>6494</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6158</v>
+        <v>6496</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>329</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6494</v>
+        <v>6497</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6496</v>
+        <v>6540</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C79">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>6497</v>
+        <v>6965</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>6540</v>
+        <v>7005</v>
       </c>
       <c r="B81">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>6935</v>
+        <v>7457</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C82">
-        <v>231</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>7005</v>
+        <v>7558</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C83">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>7457</v>
+        <v>7567</v>
       </c>
       <c r="B84">
         <v>3</v>
       </c>
       <c r="C84">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>7558</v>
+        <v>7885</v>
       </c>
       <c r="B85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C85">
-        <v>29</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>7567</v>
+        <v>7886</v>
       </c>
       <c r="B86">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C86">
-        <v>29</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>7885</v>
+        <v>8648</v>
       </c>
       <c r="B87">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>59</v>
+        <v>153</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>7886</v>
+        <v>8649</v>
       </c>
       <c r="B88">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8356</v>
+        <v>8650</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>37</v>
+        <v>102</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8648</v>
+        <v>8907</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C90">
-        <v>153</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8649</v>
+        <v>8915</v>
       </c>
       <c r="B91">
         <v>2</v>
       </c>
       <c r="C91">
-        <v>77</v>
+        <v>200</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8650</v>
+        <v>8926</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8915</v>
+        <v>8938</v>
       </c>
       <c r="B93">
         <v>2</v>
       </c>
       <c r="C93">
-        <v>67</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8938</v>
+        <v>9208</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C94">
-        <v>67</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9208</v>
+        <v>9209</v>
       </c>
       <c r="B95">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C95">
-        <v>42</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9209</v>
+        <v>9239</v>
       </c>
       <c r="B96">
         <v>29</v>
       </c>
       <c r="C96">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9239</v>
+        <v>9358</v>
       </c>
       <c r="B97">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1458,70 +1458,70 @@
         <v>2</v>
       </c>
       <c r="C98">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9910</v>
+        <v>9531</v>
       </c>
       <c r="B99">
         <v>25</v>
       </c>
       <c r="C99">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10716</v>
+        <v>9910</v>
       </c>
       <c r="B100">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C100">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10717</v>
+        <v>10149</v>
       </c>
       <c r="B101">
         <v>3</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>403</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10719</v>
+        <v>10174</v>
       </c>
       <c r="B102">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10720</v>
+        <v>10507</v>
       </c>
       <c r="B103">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10721</v>
+        <v>10716</v>
       </c>
       <c r="B104">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C104">
         <v>44</v>
@@ -1529,128 +1529,128 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10993</v>
+        <v>10717</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C105">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11150</v>
+        <v>10719</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C106">
-        <v>150</v>
+        <v>41</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11306</v>
+        <v>10720</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11396</v>
+        <v>10721</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C108">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11402</v>
+        <v>11089</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>19</v>
+        <v>71</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11403</v>
+        <v>11150</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>38</v>
+        <v>150</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11426</v>
+        <v>11306</v>
       </c>
       <c r="B111">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11492</v>
+        <v>11396</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11684</v>
+        <v>11402</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>113</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11685</v>
+        <v>11403</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>188</v>
+        <v>38</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11738</v>
+        <v>11492</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11739</v>
+        <v>11738</v>
       </c>
       <c r="B116">
         <v>2</v>
@@ -1661,18 +1661,18 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11952</v>
+        <v>11739</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>245</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12050</v>
+        <v>11895</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12128</v>
+        <v>12050</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -1694,21 +1694,21 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12489</v>
+        <v>12128</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12505</v>
+        <v>12340</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121">
         <v>7</v>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12535</v>
+        <v>12489</v>
       </c>
       <c r="B122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C122">
         <v>7</v>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12539</v>
+        <v>12505</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C123">
         <v>7</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12612</v>
+        <v>12535</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -1749,62 +1749,62 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12791</v>
+        <v>12539</v>
       </c>
       <c r="B125">
         <v>2</v>
       </c>
       <c r="C125">
-        <v>348</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12923</v>
+        <v>12597</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12924</v>
+        <v>12612</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12925</v>
+        <v>12764</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13114</v>
+        <v>12923</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13244</v>
+        <v>12924</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -1815,142 +1815,142 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13257</v>
+        <v>12925</v>
       </c>
       <c r="B131">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C131">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13258</v>
+        <v>13114</v>
       </c>
       <c r="B132">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C132">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13259</v>
+        <v>13115</v>
       </c>
       <c r="B133">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C133">
-        <v>320</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13260</v>
+        <v>13257</v>
       </c>
       <c r="B134">
         <v>29</v>
       </c>
       <c r="C134">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13264</v>
+        <v>13258</v>
       </c>
       <c r="B135">
         <v>29</v>
       </c>
       <c r="C135">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13266</v>
+        <v>13259</v>
       </c>
       <c r="B136">
         <v>29</v>
       </c>
       <c r="C136">
-        <v>47</v>
+        <v>250</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13968</v>
+        <v>13260</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C137">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>20927</v>
+        <v>13264</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C138">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21454</v>
+        <v>13266</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C139">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21793</v>
+        <v>13272</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C140">
-        <v>306</v>
+        <v>44</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>22665</v>
+        <v>13968</v>
       </c>
       <c r="B141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>23235</v>
+        <v>19996</v>
       </c>
       <c r="B142">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C142">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>23262</v>
+        <v>20223</v>
       </c>
       <c r="B143">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C143">
         <v>7</v>
@@ -1958,40 +1958,40 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>24252</v>
+        <v>20555</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>24253</v>
+        <v>21454</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C145">
-        <v>81</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>24257</v>
+        <v>22665</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146">
-        <v>60</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>24724</v>
+        <v>23262</v>
       </c>
       <c r="B147">
         <v>2</v>
@@ -2002,12 +2002,45 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
+        <v>24252</v>
+      </c>
+      <c r="B148">
+        <v>1</v>
+      </c>
+      <c r="C148">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149">
+        <v>24253</v>
+      </c>
+      <c r="B149">
+        <v>1</v>
+      </c>
+      <c r="C149">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>24724</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
         <v>25899</v>
       </c>
-      <c r="B148">
-        <v>2</v>
-      </c>
-      <c r="C148">
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151">
         <v>37</v>
       </c>
     </row>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C151"/>
+  <dimension ref="A1:C154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,13 +396,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -413,293 +413,293 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>265</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>151</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>640</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>63</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>159</v>
+        <v>214</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>356</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>215</v>
+        <v>307</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>17</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>216</v>
+        <v>345</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>307</v>
+        <v>358</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>63</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>102</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>470</v>
+        <v>417</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>593</v>
+        <v>470</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>95</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>624</v>
+        <v>590</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C20">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>823</v>
+        <v>593</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>17</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>955</v>
+        <v>616</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>957</v>
+        <v>624</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>991</v>
+        <v>823</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>997</v>
+        <v>950</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>98</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>998</v>
+        <v>955</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1012</v>
+        <v>957</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1126</v>
+        <v>1012</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28">
-        <v>95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1432</v>
+        <v>1126</v>
       </c>
       <c r="B29">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>39</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -710,7 +710,7 @@
         <v>1</v>
       </c>
       <c r="C30">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -721,158 +721,158 @@
         <v>1</v>
       </c>
       <c r="C31">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1598</v>
+        <v>1504</v>
       </c>
       <c r="B32">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="B33">
         <v>68</v>
       </c>
       <c r="C33">
-        <v>185</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B34">
         <v>68</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1654</v>
+        <v>1602</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C35">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1700</v>
+        <v>1656</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2161</v>
+        <v>1801</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2234</v>
+        <v>2161</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2328</v>
+        <v>2234</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>110</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>53</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="B42">
         <v>80</v>
       </c>
       <c r="C42">
-        <v>82</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2424</v>
+        <v>2497</v>
       </c>
       <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43">
         <v>80</v>
-      </c>
-      <c r="C43">
-        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2497</v>
+        <v>2508</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
       <c r="C44">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2508</v>
+        <v>2735</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45">
         <v>7</v>
@@ -880,219 +880,219 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2735</v>
+        <v>2774</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2736</v>
+        <v>2912</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2774</v>
+        <v>3434</v>
       </c>
       <c r="B48">
         <v>2</v>
       </c>
       <c r="C48">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2912</v>
+        <v>3451</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2934</v>
+        <v>3495</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3451</v>
+        <v>3671</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3495</v>
+        <v>3891</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>468</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3577</v>
+        <v>3892</v>
       </c>
       <c r="B53">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>37</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3670</v>
+        <v>3898</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54">
-        <v>222</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3674</v>
+        <v>3899</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C55">
-        <v>101</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3889</v>
+        <v>3909</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C56">
-        <v>48</v>
+        <v>145</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3891</v>
+        <v>4867</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3892</v>
+        <v>5152</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3893</v>
+        <v>5153</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>96</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3898</v>
+        <v>5165</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3899</v>
+        <v>5538</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3909</v>
+        <v>5539</v>
       </c>
       <c r="B62">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>295</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>4586</v>
+        <v>5541</v>
       </c>
       <c r="B63">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>614</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>4867</v>
+        <v>5577</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5152</v>
+        <v>5585</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65">
         <v>7</v>
@@ -1100,76 +1100,76 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5153</v>
+        <v>5642</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C66">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5165</v>
+        <v>5660</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5538</v>
+        <v>6097</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5539</v>
+        <v>6098</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C69">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5541</v>
+        <v>6158</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>13</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5577</v>
+        <v>6494</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5585</v>
+        <v>6496</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C72">
         <v>7</v>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5642</v>
+        <v>6497</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C73">
         <v>7</v>
@@ -1188,263 +1188,263 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5660</v>
+        <v>6540</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C74">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6158</v>
+        <v>6575</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>110</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6494</v>
+        <v>6965</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6496</v>
+        <v>7004</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6497</v>
+        <v>7005</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6540</v>
+        <v>7036</v>
       </c>
       <c r="B79">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>34</v>
+        <v>132</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>6965</v>
+        <v>7084</v>
       </c>
       <c r="B80">
         <v>3</v>
       </c>
       <c r="C80">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>7005</v>
+        <v>7457</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>7457</v>
+        <v>7558</v>
       </c>
       <c r="B82">
         <v>3</v>
       </c>
       <c r="C82">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>7558</v>
+        <v>7567</v>
       </c>
       <c r="B83">
         <v>3</v>
       </c>
       <c r="C83">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>7567</v>
+        <v>7885</v>
       </c>
       <c r="B84">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C84">
-        <v>29</v>
+        <v>64</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>7885</v>
+        <v>7886</v>
       </c>
       <c r="B85">
         <v>4</v>
       </c>
       <c r="C85">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>7886</v>
+        <v>8216</v>
       </c>
       <c r="B86">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8648</v>
+        <v>8286</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>153</v>
+        <v>220</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8649</v>
+        <v>8648</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>77</v>
+        <v>193</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8650</v>
+        <v>8649</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89">
-        <v>102</v>
+        <v>83</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8907</v>
+        <v>8688</v>
       </c>
       <c r="B90">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C90">
-        <v>12</v>
+        <v>223</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8915</v>
+        <v>8926</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>200</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8926</v>
+        <v>8938</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>27</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8938</v>
+        <v>9208</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C93">
-        <v>193</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9208</v>
+        <v>9209</v>
       </c>
       <c r="B94">
         <v>29</v>
       </c>
       <c r="C94">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9209</v>
+        <v>9358</v>
       </c>
       <c r="B95">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9239</v>
+        <v>9396</v>
       </c>
       <c r="B96">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C96">
-        <v>12</v>
+        <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9358</v>
+        <v>9531</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C97">
         <v>7</v>
@@ -1452,230 +1452,230 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>9396</v>
+        <v>9784</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>82</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9531</v>
+        <v>9910</v>
       </c>
       <c r="B99">
         <v>25</v>
       </c>
       <c r="C99">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9910</v>
+        <v>10149</v>
       </c>
       <c r="B100">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C100">
-        <v>40</v>
+        <v>434</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10149</v>
+        <v>10174</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C101">
-        <v>403</v>
+        <v>18</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10174</v>
+        <v>10716</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C102">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10507</v>
+        <v>10719</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C103">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10716</v>
+        <v>10720</v>
       </c>
       <c r="B104">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C104">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10717</v>
+        <v>10721</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C105">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>10719</v>
+        <v>10993</v>
       </c>
       <c r="B106">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>10720</v>
+        <v>11150</v>
       </c>
       <c r="B107">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>42</v>
+        <v>161</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>10721</v>
+        <v>11306</v>
       </c>
       <c r="B108">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11089</v>
+        <v>11402</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11150</v>
+        <v>11403</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>150</v>
+        <v>41</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11306</v>
+        <v>11425</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11396</v>
+        <v>11426</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C112">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11402</v>
+        <v>11467</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11403</v>
+        <v>11492</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11492</v>
+        <v>11684</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>40</v>
+        <v>283</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11738</v>
+        <v>11685</v>
       </c>
       <c r="B116">
         <v>2</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11739</v>
+        <v>11687</v>
       </c>
       <c r="B117">
         <v>2</v>
       </c>
       <c r="C117">
-        <v>7</v>
+        <v>140</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11895</v>
+        <v>11738</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C118">
         <v>7</v>
@@ -1683,51 +1683,51 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12050</v>
+        <v>11739</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12128</v>
+        <v>11844</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C120">
-        <v>19</v>
+        <v>126</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12340</v>
+        <v>11885</v>
       </c>
       <c r="B121">
         <v>2</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12489</v>
+        <v>11887</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>91</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12505</v>
+        <v>11895</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -1738,43 +1738,43 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12535</v>
+        <v>11961</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C124">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12539</v>
+        <v>12128</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12597</v>
+        <v>12304</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12612</v>
+        <v>12340</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C127">
         <v>7</v>
@@ -1782,43 +1782,43 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12764</v>
+        <v>12489</v>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>307</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12923</v>
+        <v>12505</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12924</v>
+        <v>12535</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C130">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>12925</v>
+        <v>12539</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C131">
         <v>7</v>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13114</v>
+        <v>12597</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C132">
         <v>7</v>
@@ -1837,153 +1837,153 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13115</v>
+        <v>12764</v>
       </c>
       <c r="B133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C133">
-        <v>7</v>
+        <v>331</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13257</v>
+        <v>12791</v>
       </c>
       <c r="B134">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C134">
-        <v>38</v>
+        <v>373</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13258</v>
+        <v>12923</v>
       </c>
       <c r="B135">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13259</v>
+        <v>12924</v>
       </c>
       <c r="B136">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>250</v>
+        <v>25</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13260</v>
+        <v>12925</v>
       </c>
       <c r="B137">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>13264</v>
+        <v>13257</v>
       </c>
       <c r="B138">
         <v>29</v>
       </c>
       <c r="C138">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>13266</v>
+        <v>13260</v>
       </c>
       <c r="B139">
         <v>29</v>
       </c>
       <c r="C139">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>13272</v>
+        <v>13264</v>
       </c>
       <c r="B140">
         <v>29</v>
       </c>
       <c r="C140">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>13968</v>
+        <v>13965</v>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>19996</v>
+        <v>13968</v>
       </c>
       <c r="B142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>24</v>
+        <v>46</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>20223</v>
+        <v>19686</v>
       </c>
       <c r="B143">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C143">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>20555</v>
+        <v>19687</v>
       </c>
       <c r="B144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C144">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>21454</v>
+        <v>19981</v>
       </c>
       <c r="B145">
         <v>2</v>
       </c>
       <c r="C145">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>22665</v>
+        <v>20223</v>
       </c>
       <c r="B146">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C146">
         <v>7</v>
@@ -1991,40 +1991,40 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23262</v>
+        <v>20555</v>
       </c>
       <c r="B147">
         <v>2</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>24252</v>
+        <v>20927</v>
       </c>
       <c r="B148">
         <v>1</v>
       </c>
       <c r="C148">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>24253</v>
+        <v>21454</v>
       </c>
       <c r="B149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>24724</v>
+        <v>22665</v>
       </c>
       <c r="B150">
         <v>2</v>
@@ -2035,13 +2035,46 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>25899</v>
+        <v>23262</v>
       </c>
       <c r="B151">
         <v>2</v>
       </c>
       <c r="C151">
-        <v>37</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
+        <v>23380</v>
+      </c>
+      <c r="B152">
+        <v>25</v>
+      </c>
+      <c r="C152">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>24252</v>
+      </c>
+      <c r="B153">
+        <v>1</v>
+      </c>
+      <c r="C153">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>24253</v>
+      </c>
+      <c r="B154">
+        <v>1</v>
+      </c>
+      <c r="C154">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C154"/>
+  <dimension ref="A1:C152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,7 +402,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -413,51 +413,51 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>520</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>70</v>
+        <v>520</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>71</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>70</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -468,29 +468,29 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>325</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9">
-        <v>298</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>18</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -539,153 +539,153 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>45</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>413</v>
+        <v>385</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>470</v>
+        <v>412</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19">
-        <v>16</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>590</v>
+        <v>416</v>
       </c>
       <c r="B20">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>593</v>
+        <v>474</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>103</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>616</v>
+        <v>589</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>624</v>
+        <v>590</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C23">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>823</v>
+        <v>593</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>18</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>950</v>
+        <v>616</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>955</v>
+        <v>624</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>957</v>
+        <v>823</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>49</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1012</v>
+        <v>949</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C28">
         <v>7</v>
@@ -693,230 +693,230 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1126</v>
+        <v>950</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>104</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1490</v>
+        <v>955</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1492</v>
+        <v>957</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1504</v>
+        <v>1012</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32">
-        <v>78</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1598</v>
+        <v>1309</v>
       </c>
       <c r="B33">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>71</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1601</v>
+        <v>1490</v>
       </c>
       <c r="B34">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>155</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1602</v>
+        <v>1492</v>
       </c>
       <c r="B35">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1654</v>
+        <v>1504</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1656</v>
+        <v>1598</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1801</v>
+        <v>1599</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C38">
-        <v>45</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2161</v>
+        <v>1601</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2234</v>
+        <v>1602</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C40">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2328</v>
+        <v>1801</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>139</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2424</v>
+        <v>2105</v>
       </c>
       <c r="B42">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2497</v>
+        <v>2161</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2508</v>
+        <v>2234</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2735</v>
+        <v>2328</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2774</v>
+        <v>2424</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C46">
-        <v>12</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2912</v>
+        <v>2497</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>22</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3434</v>
+        <v>2508</v>
       </c>
       <c r="B48">
         <v>2</v>
       </c>
       <c r="C48">
-        <v>68</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3451</v>
+        <v>2735</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C49">
         <v>7</v>
@@ -924,87 +924,87 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3495</v>
+        <v>2774</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3671</v>
+        <v>2912</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3891</v>
+        <v>3451</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52">
-        <v>69</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3892</v>
+        <v>3495</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3898</v>
+        <v>3671</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3899</v>
+        <v>3892</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3909</v>
+        <v>3893</v>
       </c>
       <c r="B56">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>145</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4867</v>
+        <v>3898</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57">
         <v>7</v>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5152</v>
+        <v>3899</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58">
         <v>7</v>
@@ -1023,32 +1023,32 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5153</v>
+        <v>3909</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5165</v>
+        <v>4867</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5538</v>
+        <v>5152</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61">
         <v>7</v>
@@ -1056,90 +1056,90 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5539</v>
+        <v>5153</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5541</v>
+        <v>5538</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5577</v>
+        <v>5539</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5585</v>
+        <v>5541</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5642</v>
+        <v>5577</v>
       </c>
       <c r="B66">
         <v>3</v>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5660</v>
+        <v>5585</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>122</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>6097</v>
+        <v>5642</v>
       </c>
       <c r="B68">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>6098</v>
+        <v>5660</v>
       </c>
       <c r="B69">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>6494</v>
+        <v>6496</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -1166,120 +1166,120 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6496</v>
+        <v>6575</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>7</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>6497</v>
+        <v>6630</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>6540</v>
+        <v>6936</v>
       </c>
       <c r="B74">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>37</v>
+        <v>123</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6575</v>
+        <v>7558</v>
       </c>
       <c r="B75">
         <v>3</v>
       </c>
       <c r="C75">
-        <v>162</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6965</v>
+        <v>7567</v>
       </c>
       <c r="B76">
         <v>3</v>
       </c>
       <c r="C76">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>7004</v>
+        <v>7885</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C77">
-        <v>35</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>7005</v>
+        <v>8216</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>7036</v>
+        <v>8217</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C79">
-        <v>132</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>7084</v>
+        <v>8648</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>59</v>
+        <v>138</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>7457</v>
+        <v>8649</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>8</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>7558</v>
+        <v>8926</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C82">
         <v>7</v>
@@ -1287,164 +1287,164 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>7567</v>
+        <v>8938</v>
       </c>
       <c r="B83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>32</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>7885</v>
+        <v>9182</v>
       </c>
       <c r="B84">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>7886</v>
+        <v>9209</v>
       </c>
       <c r="B85">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C85">
-        <v>65</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8216</v>
+        <v>9358</v>
       </c>
       <c r="B86">
         <v>1</v>
       </c>
       <c r="C86">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8286</v>
+        <v>9396</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>220</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8648</v>
+        <v>9530</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C88">
-        <v>193</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8649</v>
+        <v>9531</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C89">
-        <v>83</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8688</v>
+        <v>9997</v>
       </c>
       <c r="B90">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="C90">
-        <v>223</v>
+        <v>61</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8926</v>
+        <v>10149</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C91">
-        <v>7</v>
+        <v>435</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8938</v>
+        <v>10507</v>
       </c>
       <c r="B92">
         <v>2</v>
       </c>
       <c r="C92">
-        <v>72</v>
+        <v>34</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>9208</v>
+        <v>10616</v>
       </c>
       <c r="B93">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9209</v>
+        <v>10716</v>
       </c>
       <c r="B94">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C94">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9358</v>
+        <v>10719</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C95">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9396</v>
+        <v>10721</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C96">
-        <v>93</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9531</v>
+        <v>10993</v>
       </c>
       <c r="B97">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C97">
         <v>7</v>
@@ -1452,230 +1452,230 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>9784</v>
+        <v>11039</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9910</v>
+        <v>11059</v>
       </c>
       <c r="B99">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C99">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10149</v>
+        <v>11089</v>
       </c>
       <c r="B100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>434</v>
+        <v>78</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10174</v>
+        <v>11150</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10716</v>
+        <v>11226</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10719</v>
+        <v>11306</v>
       </c>
       <c r="B103">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10720</v>
+        <v>11402</v>
       </c>
       <c r="B104">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10721</v>
+        <v>11403</v>
       </c>
       <c r="B105">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>10993</v>
+        <v>11426</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C106">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11150</v>
+        <v>11467</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>161</v>
+        <v>47</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11306</v>
+        <v>11492</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11402</v>
+        <v>11681</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C109">
-        <v>7</v>
+        <v>201</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11403</v>
+        <v>11685</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>41</v>
+        <v>201</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11425</v>
+        <v>11738</v>
       </c>
       <c r="B111">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>54</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11426</v>
+        <v>11739</v>
       </c>
       <c r="B112">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>54</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11467</v>
+        <v>11885</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>45</v>
+        <v>88</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11492</v>
+        <v>11887</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>10</v>
+        <v>88</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11684</v>
+        <v>11895</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>283</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11685</v>
+        <v>11961</v>
       </c>
       <c r="B116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11687</v>
+        <v>11965</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>140</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11738</v>
+        <v>12050</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C118">
         <v>7</v>
@@ -1683,54 +1683,54 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11739</v>
+        <v>12128</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C119">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11844</v>
+        <v>12304</v>
       </c>
       <c r="B120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>126</v>
+        <v>52</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>11885</v>
+        <v>12340</v>
       </c>
       <c r="B121">
         <v>2</v>
       </c>
       <c r="C121">
-        <v>90</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>11887</v>
+        <v>12505</v>
       </c>
       <c r="B122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C122">
-        <v>91</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>11895</v>
+        <v>12535</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123">
         <v>7</v>
@@ -1738,40 +1738,40 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>11961</v>
+        <v>12539</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12128</v>
+        <v>12543</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12304</v>
+        <v>12544</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12340</v>
+        <v>12597</v>
       </c>
       <c r="B127">
         <v>2</v>
@@ -1782,32 +1782,32 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12489</v>
+        <v>12764</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>331</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12505</v>
+        <v>12791</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>376</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12535</v>
+        <v>12925</v>
       </c>
       <c r="B130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C130">
         <v>7</v>
@@ -1815,216 +1815,216 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>12539</v>
+        <v>13030</v>
       </c>
       <c r="B131">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>112</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>12597</v>
+        <v>13257</v>
       </c>
       <c r="B132">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C132">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>12764</v>
+        <v>13259</v>
       </c>
       <c r="B133">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C133">
-        <v>331</v>
+        <v>350</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>12791</v>
+        <v>13264</v>
       </c>
       <c r="B134">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C134">
-        <v>373</v>
+        <v>33</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>12923</v>
+        <v>13269</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C135">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>12924</v>
+        <v>13965</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>12925</v>
+        <v>13968</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>13257</v>
+        <v>19686</v>
       </c>
       <c r="B138">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C138">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>13260</v>
+        <v>19981</v>
       </c>
       <c r="B139">
+        <v>2</v>
+      </c>
+      <c r="C139">
         <v>29</v>
-      </c>
-      <c r="C139">
-        <v>33</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>13264</v>
+        <v>19983</v>
       </c>
       <c r="B140">
+        <v>2</v>
+      </c>
+      <c r="C140">
         <v>29</v>
-      </c>
-      <c r="C140">
-        <v>33</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>13965</v>
+        <v>20220</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C141">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>13968</v>
+        <v>20223</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C142">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>19686</v>
+        <v>20555</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C143">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>19687</v>
+        <v>20927</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>19981</v>
+        <v>21454</v>
       </c>
       <c r="B145">
         <v>2</v>
       </c>
       <c r="C145">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>20223</v>
+        <v>21793</v>
       </c>
       <c r="B146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>7</v>
+        <v>250</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>20555</v>
+        <v>22325</v>
       </c>
       <c r="B147">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>20927</v>
+        <v>22665</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C148">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>21454</v>
+        <v>23235</v>
       </c>
       <c r="B149">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C149">
-        <v>8</v>
+        <v>37</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>22665</v>
+        <v>23262</v>
       </c>
       <c r="B150">
         <v>2</v>
@@ -2035,10 +2035,10 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>23262</v>
+        <v>24252</v>
       </c>
       <c r="B151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C151">
         <v>7</v>
@@ -2046,34 +2046,12 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>23380</v>
+        <v>24253</v>
       </c>
       <c r="B152">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C152">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153">
-        <v>24252</v>
-      </c>
-      <c r="B153">
-        <v>1</v>
-      </c>
-      <c r="C153">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154">
-        <v>24253</v>
-      </c>
-      <c r="B154">
-        <v>1</v>
-      </c>
-      <c r="C154">
         <v>7</v>
       </c>
     </row>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
@@ -396,35 +396,35 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>53</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4">
-        <v>98</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -440,24 +440,24 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -473,98 +473,98 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9">
-        <v>147</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>301</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>216</v>
+        <v>307</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>307</v>
+        <v>358</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>68</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>196</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>358</v>
+        <v>417</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>361</v>
+        <v>583</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>378</v>
+        <v>589</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>83</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>385</v>
+        <v>590</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C17">
         <v>45</v>
@@ -572,120 +572,120 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>410</v>
+        <v>616</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>412</v>
+        <v>624</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>416</v>
+        <v>823</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>474</v>
+        <v>950</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>589</v>
+        <v>1007</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>61</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>590</v>
+        <v>1012</v>
       </c>
       <c r="B23">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>593</v>
+        <v>1124</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>103</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>616</v>
+        <v>1126</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>46</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>624</v>
+        <v>1309</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>823</v>
+        <v>1490</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>949</v>
+        <v>1492</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C28">
         <v>7</v>
@@ -693,43 +693,43 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>950</v>
+        <v>1504</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>27</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>955</v>
+        <v>1598</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C30">
-        <v>49</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>957</v>
+        <v>1601</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C31">
-        <v>49</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1012</v>
+        <v>1602</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C32">
         <v>7</v>
@@ -737,216 +737,216 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1309</v>
+        <v>1656</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1490</v>
+        <v>1801</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1492</v>
+        <v>2049</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>17</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1504</v>
+        <v>2161</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>79</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1598</v>
+        <v>2234</v>
       </c>
       <c r="B37">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>71</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1599</v>
+        <v>2328</v>
       </c>
       <c r="B38">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>142</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1601</v>
+        <v>2423</v>
       </c>
       <c r="B39">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C39">
-        <v>178</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1602</v>
+        <v>2424</v>
       </c>
       <c r="B40">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1801</v>
+        <v>2497</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>47</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2105</v>
+        <v>2508</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>137</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2161</v>
+        <v>2735</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2234</v>
+        <v>2774</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2328</v>
+        <v>2803</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45">
-        <v>139</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2424</v>
+        <v>2912</v>
       </c>
       <c r="B46">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>129</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2497</v>
+        <v>3451</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>82</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2508</v>
+        <v>3495</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2735</v>
+        <v>3575</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2774</v>
+        <v>3576</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C50">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2912</v>
+        <v>3577</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C51">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3451</v>
+        <v>3891</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -957,65 +957,65 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3495</v>
+        <v>3892</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3671</v>
+        <v>3893</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3892</v>
+        <v>3898</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C55">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3893</v>
+        <v>3899</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3898</v>
+        <v>3955</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3899</v>
+        <v>4867</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C58">
         <v>7</v>
@@ -1023,21 +1023,21 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3909</v>
+        <v>5111</v>
       </c>
       <c r="B59">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>110</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>4867</v>
+        <v>5152</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60">
         <v>7</v>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5152</v>
+        <v>5153</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5153</v>
+        <v>5491</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1117,7 +1117,7 @@
         <v>3</v>
       </c>
       <c r="C67">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1144,142 +1144,142 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>6158</v>
+        <v>6097</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C70">
-        <v>122</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>6496</v>
+        <v>6098</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6575</v>
+        <v>6158</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>162</v>
+        <v>122</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>6630</v>
+        <v>6494</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>48</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>6936</v>
+        <v>6497</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>123</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>7558</v>
+        <v>6575</v>
       </c>
       <c r="B75">
         <v>3</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>7567</v>
+        <v>6872</v>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C76">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>7885</v>
+        <v>6936</v>
       </c>
       <c r="B77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>64</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8216</v>
+        <v>7004</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8217</v>
+        <v>7084</v>
       </c>
       <c r="B79">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>8</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8648</v>
+        <v>7558</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>138</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8649</v>
+        <v>7567</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81">
-        <v>83</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8926</v>
+        <v>7885</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C82">
         <v>7</v>
@@ -1287,164 +1287,164 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8938</v>
+        <v>8216</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>73</v>
+        <v>40</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>9182</v>
+        <v>8356</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84">
-        <v>74</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>9209</v>
+        <v>8648</v>
       </c>
       <c r="B85">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>15</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>9358</v>
+        <v>8649</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>9396</v>
+        <v>8650</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>88</v>
+        <v>138</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>9530</v>
+        <v>8688</v>
       </c>
       <c r="B88">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C88">
-        <v>31</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>9531</v>
+        <v>8938</v>
       </c>
       <c r="B89">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9997</v>
+        <v>9209</v>
       </c>
       <c r="B90">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="C90">
-        <v>61</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>10149</v>
+        <v>9396</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>435</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>10507</v>
+        <v>9507</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C92">
-        <v>34</v>
+        <v>123</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>10616</v>
+        <v>9531</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C93">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>10716</v>
+        <v>9910</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10719</v>
+        <v>10149</v>
       </c>
       <c r="B95">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C95">
-        <v>47</v>
+        <v>434</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>10721</v>
+        <v>10174</v>
       </c>
       <c r="B96">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10993</v>
+        <v>10716</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C97">
         <v>7</v>
@@ -1452,76 +1452,76 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>11039</v>
+        <v>10717</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C98">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>11059</v>
+        <v>10719</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C99">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>11089</v>
+        <v>10993</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100">
-        <v>78</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11150</v>
+        <v>11089</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C101">
-        <v>161</v>
+        <v>76</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11226</v>
+        <v>11150</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>21</v>
+        <v>159</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11306</v>
+        <v>11234</v>
       </c>
       <c r="B103">
         <v>2</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11402</v>
+        <v>11306</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11403</v>
+        <v>11396</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105">
         <v>41</v>
@@ -1540,139 +1540,139 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11426</v>
+        <v>11402</v>
       </c>
       <c r="B106">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>54</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11467</v>
+        <v>11403</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11492</v>
+        <v>11425</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C108">
-        <v>10</v>
+        <v>54</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11681</v>
+        <v>11467</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>201</v>
+        <v>46</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11685</v>
+        <v>11492</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>201</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11738</v>
+        <v>11681</v>
       </c>
       <c r="B111">
         <v>2</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>283</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11739</v>
+        <v>11684</v>
       </c>
       <c r="B112">
         <v>2</v>
       </c>
       <c r="C112">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11885</v>
+        <v>11685</v>
       </c>
       <c r="B113">
         <v>2</v>
       </c>
       <c r="C113">
-        <v>88</v>
+        <v>200</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11887</v>
+        <v>11687</v>
       </c>
       <c r="B114">
         <v>2</v>
       </c>
       <c r="C114">
-        <v>88</v>
+        <v>144</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11895</v>
+        <v>11739</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11961</v>
+        <v>11844</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116">
-        <v>25</v>
+        <v>125</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11965</v>
+        <v>11887</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>20</v>
+        <v>88</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12050</v>
+        <v>11895</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -1683,32 +1683,32 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12128</v>
+        <v>11961</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12304</v>
+        <v>12010</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C120">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12340</v>
+        <v>12050</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C121">
         <v>7</v>
@@ -1716,32 +1716,32 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12505</v>
+        <v>12128</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12535</v>
+        <v>12304</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C123">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12539</v>
+        <v>12505</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -1749,7 +1749,7 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12543</v>
+        <v>12535</v>
       </c>
       <c r="B125">
         <v>2</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12544</v>
+        <v>12539</v>
       </c>
       <c r="B126">
         <v>2</v>
@@ -1782,178 +1782,178 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12764</v>
+        <v>12791</v>
       </c>
       <c r="B128">
         <v>2</v>
       </c>
       <c r="C128">
-        <v>331</v>
+        <v>375</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12791</v>
+        <v>12923</v>
       </c>
       <c r="B129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C129">
-        <v>376</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12925</v>
+        <v>12924</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13030</v>
+        <v>12925</v>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C131">
-        <v>112</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13257</v>
+        <v>13243</v>
       </c>
       <c r="B132">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C132">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13259</v>
+        <v>13244</v>
       </c>
       <c r="B133">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C133">
-        <v>350</v>
+        <v>23</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13264</v>
+        <v>13257</v>
       </c>
       <c r="B134">
         <v>29</v>
       </c>
       <c r="C134">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13269</v>
+        <v>13259</v>
       </c>
       <c r="B135">
         <v>29</v>
       </c>
       <c r="C135">
-        <v>35</v>
+        <v>350</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13965</v>
+        <v>13260</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C136">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13968</v>
+        <v>13264</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C137">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>19686</v>
+        <v>13962</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>14</v>
+        <v>46</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>19981</v>
+        <v>13965</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C139">
-        <v>29</v>
+        <v>47</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>19983</v>
+        <v>13968</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>29</v>
+        <v>46</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>20220</v>
+        <v>19686</v>
       </c>
       <c r="B141">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>20223</v>
+        <v>19981</v>
       </c>
       <c r="B142">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C142">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>20555</v>
+        <v>20223</v>
       </c>
       <c r="B143">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C143">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -1980,54 +1980,54 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>21793</v>
+        <v>21798</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146">
-        <v>250</v>
+        <v>63</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>22325</v>
+        <v>22665</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C147">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>22665</v>
+        <v>23235</v>
       </c>
       <c r="B148">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C148">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>23235</v>
+        <v>23262</v>
       </c>
       <c r="B149">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C149">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>23262</v>
+        <v>24252</v>
       </c>
       <c r="B150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C150">
         <v>7</v>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>24252</v>
+        <v>24253</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2046,13 +2046,13 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>24253</v>
+        <v>24724</v>
       </c>
       <c r="B152">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C152">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C152"/>
+  <dimension ref="A1:C160"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,232 +402,232 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>53</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>99</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>62</v>
+        <v>159</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4">
-        <v>359</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>84</v>
+        <v>345</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>520</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>144</v>
+        <v>346</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>70</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>146</v>
+        <v>405</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>70</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>159</v>
+        <v>408</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>214</v>
+        <v>413</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>304</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>215</v>
+        <v>474</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>307</v>
+        <v>949</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>69</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>358</v>
+        <v>990</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>378</v>
+        <v>1012</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>83</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>417</v>
+        <v>1309</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>165</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>583</v>
+        <v>1598</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C15">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>589</v>
+        <v>1601</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>590</v>
+        <v>1602</v>
       </c>
       <c r="B17">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="C17">
-        <v>45</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>616</v>
+        <v>2049</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>46</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>624</v>
+        <v>2108</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>46</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>823</v>
+        <v>2161</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>950</v>
+        <v>2188</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>1007</v>
+        <v>2322</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>121</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1012</v>
+        <v>2323</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -638,98 +638,98 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>1124</v>
+        <v>2328</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>84</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>1126</v>
+        <v>2331</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>99</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>1309</v>
+        <v>2418</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C26">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1490</v>
+        <v>2423</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C27">
-        <v>23</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1492</v>
+        <v>2424</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1504</v>
+        <v>2504</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>78</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1598</v>
+        <v>2505</v>
       </c>
       <c r="B30">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="C30">
-        <v>71</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1601</v>
+        <v>2506</v>
       </c>
       <c r="B31">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="C31">
-        <v>177</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1602</v>
+        <v>2508</v>
       </c>
       <c r="B32">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C32">
         <v>7</v>
@@ -737,142 +737,142 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1656</v>
+        <v>2734</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1801</v>
+        <v>2774</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2049</v>
+        <v>2803</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>250</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2161</v>
+        <v>3071</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2234</v>
+        <v>3073</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2328</v>
+        <v>3080</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>59</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2423</v>
+        <v>3131</v>
       </c>
       <c r="B39">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="C39">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2424</v>
+        <v>3379</v>
       </c>
       <c r="B40">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>129</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2497</v>
+        <v>3495</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>82</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2508</v>
+        <v>3576</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2735</v>
+        <v>3581</v>
       </c>
       <c r="B43">
         <v>3</v>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2774</v>
+        <v>3582</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2803</v>
+        <v>3584</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45">
         <v>7</v>
@@ -880,18 +880,18 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2912</v>
+        <v>3585</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>3451</v>
+        <v>3892</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -902,54 +902,54 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3495</v>
+        <v>3898</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3575</v>
+        <v>3906</v>
       </c>
       <c r="B49">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C49">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3576</v>
+        <v>4030</v>
       </c>
       <c r="B50">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C50">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3577</v>
+        <v>4592</v>
       </c>
       <c r="B51">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3891</v>
+        <v>4594</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C52">
         <v>7</v>
@@ -957,7 +957,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3892</v>
+        <v>4672</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -968,32 +968,32 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3893</v>
+        <v>4867</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54">
-        <v>54</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3898</v>
+        <v>5005</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3899</v>
+        <v>5076</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C56">
         <v>7</v>
@@ -1001,54 +1001,54 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3955</v>
+        <v>5152</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4867</v>
+        <v>5209</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>251</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5111</v>
+        <v>5243</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C59">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5152</v>
+        <v>5490</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5153</v>
+        <v>5538</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61">
         <v>7</v>
@@ -1056,351 +1056,351 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5491</v>
+        <v>5539</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5538</v>
+        <v>5541</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5539</v>
+        <v>5577</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C64">
-        <v>13</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5541</v>
+        <v>5584</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C65">
-        <v>13</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5577</v>
+        <v>5585</v>
       </c>
       <c r="B66">
         <v>3</v>
       </c>
       <c r="C66">
-        <v>8</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5585</v>
+        <v>5660</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>121</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5642</v>
+        <v>5812</v>
       </c>
       <c r="B68">
         <v>3</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>266</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5660</v>
+        <v>6158</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>6097</v>
+        <v>6294</v>
       </c>
       <c r="B70">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>6098</v>
+        <v>6575</v>
       </c>
       <c r="B71">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C71">
-        <v>34</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6158</v>
+        <v>6630</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>122</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>6494</v>
+        <v>6935</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>23</v>
+        <v>160</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>6497</v>
+        <v>6946</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6575</v>
+        <v>7363</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>162</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6872</v>
+        <v>7517</v>
       </c>
       <c r="B76">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6936</v>
+        <v>7673</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C77">
-        <v>124</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>7004</v>
+        <v>8156</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C78">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>7084</v>
+        <v>8187</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C79">
-        <v>77</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>7558</v>
+        <v>8286</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>7</v>
+        <v>228</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>7567</v>
+        <v>8650</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>32</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>7885</v>
+        <v>8943</v>
       </c>
       <c r="B82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C82">
-        <v>7</v>
+        <v>175</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8216</v>
+        <v>9070</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8356</v>
+        <v>9396</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>39</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8648</v>
+        <v>9531</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C85">
-        <v>138</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8649</v>
+        <v>9778</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8650</v>
+        <v>9840</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C87">
-        <v>138</v>
+        <v>336</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8688</v>
+        <v>9854</v>
       </c>
       <c r="B88">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>170</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8938</v>
+        <v>10149</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C89">
-        <v>73</v>
+        <v>425</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9209</v>
+        <v>10161</v>
       </c>
       <c r="B90">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9396</v>
+        <v>10595</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C91">
-        <v>88</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9507</v>
+        <v>10596</v>
       </c>
       <c r="B92">
         <v>3</v>
       </c>
       <c r="C92">
-        <v>123</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>9531</v>
+        <v>10598</v>
       </c>
       <c r="B93">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -1408,43 +1408,43 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9910</v>
+        <v>10599</v>
       </c>
       <c r="B94">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C94">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10149</v>
+        <v>10616</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>434</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>10174</v>
+        <v>10717</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C96">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10716</v>
+        <v>11216</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C97">
         <v>7</v>
@@ -1452,95 +1452,95 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10717</v>
+        <v>11421</v>
       </c>
       <c r="B98">
         <v>3</v>
       </c>
       <c r="C98">
-        <v>55</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10719</v>
+        <v>11467</v>
       </c>
       <c r="B99">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10993</v>
+        <v>11492</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11089</v>
+        <v>11641</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>76</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11150</v>
+        <v>11681</v>
       </c>
       <c r="B102">
         <v>2</v>
       </c>
       <c r="C102">
-        <v>159</v>
+        <v>121</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11234</v>
+        <v>11685</v>
       </c>
       <c r="B103">
         <v>2</v>
       </c>
       <c r="C103">
-        <v>84</v>
+        <v>319</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11306</v>
+        <v>11737</v>
       </c>
       <c r="B104">
         <v>2</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11396</v>
+        <v>11738</v>
       </c>
       <c r="B105">
         <v>2</v>
       </c>
       <c r="C105">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11402</v>
+        <v>11895</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -1551,164 +1551,164 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11403</v>
+        <v>11911</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11425</v>
+        <v>11944</v>
       </c>
       <c r="B108">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C108">
-        <v>54</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11467</v>
+        <v>11967</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>46</v>
+        <v>62</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11492</v>
+        <v>11973</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C110">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11681</v>
+        <v>11974</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C111">
-        <v>283</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11684</v>
+        <v>12028</v>
       </c>
       <c r="B112">
         <v>2</v>
       </c>
       <c r="C112">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11685</v>
+        <v>12128</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>200</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11687</v>
+        <v>12243</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C114">
-        <v>144</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11739</v>
+        <v>12250</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C115">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11844</v>
+        <v>12253</v>
       </c>
       <c r="B116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C116">
-        <v>125</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11887</v>
+        <v>12270</v>
       </c>
       <c r="B117">
         <v>2</v>
       </c>
       <c r="C117">
-        <v>88</v>
+        <v>31</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11895</v>
+        <v>12304</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11961</v>
+        <v>12489</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12010</v>
+        <v>12505</v>
       </c>
       <c r="B120">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>72</v>
+        <v>32</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12050</v>
+        <v>12535</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121">
         <v>7</v>
@@ -1716,32 +1716,32 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12128</v>
+        <v>12538</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C122">
-        <v>21</v>
+        <v>209</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12304</v>
+        <v>12539</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12505</v>
+        <v>12595</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -1749,73 +1749,73 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12535</v>
+        <v>12764</v>
       </c>
       <c r="B125">
         <v>2</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>345</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12539</v>
+        <v>12791</v>
       </c>
       <c r="B126">
         <v>2</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>379</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12597</v>
+        <v>12904</v>
       </c>
       <c r="B127">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12791</v>
+        <v>12925</v>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>375</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12923</v>
+        <v>13023</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>444</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12924</v>
+        <v>13030</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>23</v>
+        <v>93</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>12925</v>
+        <v>13045</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -1826,134 +1826,134 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13243</v>
+        <v>13109</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>23</v>
+        <v>312</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13244</v>
+        <v>13116</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13257</v>
+        <v>13244</v>
       </c>
       <c r="B134">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13259</v>
+        <v>13293</v>
       </c>
       <c r="B135">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C135">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13260</v>
+        <v>13407</v>
       </c>
       <c r="B136">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C136">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13264</v>
+        <v>13462</v>
       </c>
       <c r="B137">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>32</v>
+        <v>60</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>13962</v>
+        <v>19879</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>13965</v>
+        <v>19966</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C139">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>13968</v>
+        <v>19981</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C140">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>19686</v>
+        <v>20555</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>19981</v>
+        <v>20556</v>
       </c>
       <c r="B142">
         <v>2</v>
       </c>
       <c r="C142">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>20223</v>
+        <v>20650</v>
       </c>
       <c r="B143">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C143">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -1964,67 +1964,67 @@
         <v>1</v>
       </c>
       <c r="C144">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>21454</v>
+        <v>20953</v>
       </c>
       <c r="B145">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C145">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>21798</v>
+        <v>21704</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C146">
-        <v>63</v>
+        <v>685</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>22665</v>
+        <v>21710</v>
       </c>
       <c r="B147">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>269</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>23235</v>
+        <v>21773</v>
       </c>
       <c r="B148">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C148">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>23262</v>
+        <v>22316</v>
       </c>
       <c r="B149">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C149">
-        <v>7</v>
+        <v>141</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>24252</v>
+        <v>22361</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2035,10 +2035,10 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>24253</v>
+        <v>22573</v>
       </c>
       <c r="B151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C151">
         <v>7</v>
@@ -2046,13 +2046,101 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
+        <v>23262</v>
+      </c>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>23488</v>
+      </c>
+      <c r="B153">
+        <v>3</v>
+      </c>
+      <c r="C153">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>24121</v>
+      </c>
+      <c r="B154">
+        <v>3</v>
+      </c>
+      <c r="C154">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155">
+        <v>24252</v>
+      </c>
+      <c r="B155">
+        <v>1</v>
+      </c>
+      <c r="C155">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156">
+        <v>24253</v>
+      </c>
+      <c r="B156">
+        <v>1</v>
+      </c>
+      <c r="C156">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157">
+        <v>24256</v>
+      </c>
+      <c r="B157">
+        <v>1</v>
+      </c>
+      <c r="C157">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158">
+        <v>24257</v>
+      </c>
+      <c r="B158">
+        <v>1</v>
+      </c>
+      <c r="C158">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159">
+        <v>24707</v>
+      </c>
+      <c r="B159">
+        <v>3</v>
+      </c>
+      <c r="C159">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160">
         <v>24724</v>
       </c>
-      <c r="B152">
-        <v>2</v>
-      </c>
-      <c r="C152">
-        <v>26</v>
+      <c r="B160">
+        <v>2</v>
+      </c>
+      <c r="C160">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C160"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -418,46 +418,46 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>338</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>345</v>
+        <v>159</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5">
-        <v>142</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>346</v>
+        <v>192</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6">
-        <v>272</v>
+        <v>675</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>405</v>
+        <v>216</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>290</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -468,287 +468,287 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>949</v>
+        <v>523</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>990</v>
+        <v>590</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>24</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>1012</v>
+        <v>949</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>1309</v>
+        <v>1007</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>25</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>1598</v>
+        <v>1012</v>
       </c>
       <c r="B15">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>1601</v>
+        <v>1309</v>
       </c>
       <c r="B16">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>95</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>1602</v>
+        <v>1598</v>
       </c>
       <c r="B17">
         <v>68</v>
       </c>
       <c r="C17">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>2049</v>
+        <v>1601</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C18">
-        <v>249</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>2108</v>
+        <v>1602</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C19">
-        <v>120</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2161</v>
+        <v>1655</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2188</v>
+        <v>1691</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>2322</v>
+        <v>2057</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>50</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>2323</v>
+        <v>2108</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>2328</v>
+        <v>2161</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>2331</v>
+        <v>2188</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>2418</v>
+        <v>2193</v>
       </c>
       <c r="B26">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>2423</v>
+        <v>2194</v>
       </c>
       <c r="B27">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>87</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>2424</v>
+        <v>2323</v>
       </c>
       <c r="B28">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>78</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>2504</v>
+        <v>2331</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>12</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>2505</v>
+        <v>2423</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>2506</v>
+        <v>2424</v>
       </c>
       <c r="B31">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>2508</v>
+        <v>2497</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2734</v>
+        <v>2505</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C33">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2774</v>
+        <v>2508</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -759,109 +759,109 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2803</v>
+        <v>2774</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35">
-        <v>110</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>3071</v>
+        <v>2775</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>3073</v>
+        <v>2778</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>3080</v>
+        <v>2803</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>3131</v>
+        <v>3073</v>
       </c>
       <c r="B39">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C39">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>3379</v>
+        <v>3080</v>
       </c>
       <c r="B40">
         <v>3</v>
       </c>
       <c r="C40">
-        <v>36</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>3495</v>
+        <v>3131</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C41">
-        <v>16</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>3576</v>
+        <v>3495</v>
       </c>
       <c r="B42">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>45</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>3581</v>
+        <v>3584</v>
       </c>
       <c r="B43">
         <v>3</v>
       </c>
       <c r="C43">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>3582</v>
+        <v>3670</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44">
         <v>7</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>3584</v>
+        <v>3892</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C45">
         <v>7</v>
@@ -880,7 +880,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>3585</v>
+        <v>3898</v>
       </c>
       <c r="B46">
         <v>3</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>3892</v>
+        <v>3906</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C47">
         <v>7</v>
@@ -902,21 +902,21 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3898</v>
+        <v>3909</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3906</v>
+        <v>4592</v>
       </c>
       <c r="B49">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C49">
         <v>7</v>
@@ -924,87 +924,87 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>4030</v>
+        <v>4594</v>
       </c>
       <c r="B50">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>4592</v>
+        <v>4672</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>4594</v>
+        <v>4867</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>4672</v>
+        <v>5111</v>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>4867</v>
+        <v>5152</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>5005</v>
+        <v>5208</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C55">
-        <v>149</v>
+        <v>254</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>5076</v>
+        <v>5209</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>5152</v>
+        <v>5243</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57">
         <v>7</v>
@@ -1012,189 +1012,189 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5209</v>
+        <v>5538</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>251</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5243</v>
+        <v>5539</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5490</v>
+        <v>5541</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5538</v>
+        <v>5577</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>7</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5539</v>
+        <v>5585</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C62">
-        <v>13</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5541</v>
+        <v>5660</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5577</v>
+        <v>6158</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>99</v>
+        <v>305</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5584</v>
+        <v>6292</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>118</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5585</v>
+        <v>6294</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>121</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5660</v>
+        <v>6494</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5812</v>
+        <v>6540</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C68">
-        <v>266</v>
+        <v>37</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>6158</v>
+        <v>6575</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>123</v>
+        <v>403</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>6294</v>
+        <v>6630</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>6575</v>
+        <v>6936</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>121</v>
+        <v>160</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6630</v>
+        <v>6946</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>6935</v>
+        <v>7004</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>160</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>6946</v>
+        <v>7084</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1232,183 +1232,183 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8156</v>
+        <v>7886</v>
       </c>
       <c r="B78">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C78">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8187</v>
+        <v>8156</v>
       </c>
       <c r="B79">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C79">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8286</v>
+        <v>8217</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C80">
-        <v>228</v>
+        <v>197</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8650</v>
+        <v>8285</v>
       </c>
       <c r="B81">
         <v>2</v>
       </c>
       <c r="C81">
-        <v>84</v>
+        <v>227</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8943</v>
+        <v>8677</v>
       </c>
       <c r="B82">
         <v>3</v>
       </c>
       <c r="C82">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>9070</v>
+        <v>8926</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83">
-        <v>15</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>9396</v>
+        <v>8927</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C84">
-        <v>87</v>
+        <v>996</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>9531</v>
+        <v>8943</v>
       </c>
       <c r="B85">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C85">
-        <v>7</v>
+        <v>178</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>9778</v>
+        <v>8944</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C86">
-        <v>21</v>
+        <v>101</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>9840</v>
+        <v>9070</v>
       </c>
       <c r="B87">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>336</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>9854</v>
+        <v>9122</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C88">
-        <v>88</v>
+        <v>129</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>10149</v>
+        <v>9357</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>425</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>10161</v>
+        <v>9358</v>
       </c>
       <c r="B90">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>10595</v>
+        <v>9396</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>8</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>10596</v>
+        <v>9507</v>
       </c>
       <c r="B92">
         <v>3</v>
       </c>
       <c r="C92">
-        <v>7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>10598</v>
+        <v>10149</v>
       </c>
       <c r="B93">
         <v>3</v>
       </c>
       <c r="C93">
-        <v>7</v>
+        <v>428</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>10599</v>
+        <v>10161</v>
       </c>
       <c r="B94">
         <v>3</v>
@@ -1419,18 +1419,18 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10616</v>
+        <v>10596</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C95">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>10717</v>
+        <v>10599</v>
       </c>
       <c r="B96">
         <v>3</v>
@@ -1441,175 +1441,175 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>11216</v>
+        <v>10616</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>11421</v>
+        <v>10717</v>
       </c>
       <c r="B98">
         <v>3</v>
       </c>
       <c r="C98">
-        <v>7</v>
+        <v>56</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>11467</v>
+        <v>10993</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>11492</v>
+        <v>11093</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11641</v>
+        <v>11150</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>160</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11681</v>
+        <v>11216</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>121</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11685</v>
+        <v>11402</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>319</v>
+        <v>49</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11737</v>
+        <v>11403</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11738</v>
+        <v>11492</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11895</v>
+        <v>11737</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11911</v>
+        <v>11738</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11944</v>
+        <v>11739</v>
       </c>
       <c r="B108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11967</v>
+        <v>11767</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11973</v>
+        <v>11844</v>
       </c>
       <c r="B110">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>124</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11974</v>
+        <v>11895</v>
       </c>
       <c r="B111">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>12028</v>
+        <v>11911</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112">
         <v>7</v>
@@ -1617,32 +1617,32 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>12128</v>
+        <v>11944</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C113">
-        <v>21</v>
+        <v>280</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>12243</v>
+        <v>11967</v>
       </c>
       <c r="B114">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>8</v>
+        <v>99</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>12250</v>
+        <v>11973</v>
       </c>
       <c r="B115">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C115">
         <v>7</v>
@@ -1650,87 +1650,87 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12253</v>
+        <v>11974</v>
       </c>
       <c r="B116">
         <v>3</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12270</v>
+        <v>12128</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12304</v>
+        <v>12269</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>52</v>
+        <v>31</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12489</v>
+        <v>12270</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12505</v>
+        <v>12304</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12535</v>
+        <v>12340</v>
       </c>
       <c r="B121">
         <v>2</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12538</v>
+        <v>12489</v>
       </c>
       <c r="B122">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C122">
-        <v>209</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12539</v>
+        <v>12505</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C123">
         <v>7</v>
@@ -1738,68 +1738,68 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12595</v>
+        <v>12535</v>
       </c>
       <c r="B124">
         <v>2</v>
       </c>
       <c r="C124">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12764</v>
+        <v>12539</v>
       </c>
       <c r="B125">
         <v>2</v>
       </c>
       <c r="C125">
-        <v>345</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12791</v>
+        <v>12595</v>
       </c>
       <c r="B126">
         <v>2</v>
       </c>
       <c r="C126">
-        <v>379</v>
+        <v>28</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12904</v>
+        <v>12791</v>
       </c>
       <c r="B127">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C127">
-        <v>8</v>
+        <v>376</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12925</v>
+        <v>12904</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>355</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13023</v>
+        <v>12925</v>
       </c>
       <c r="B129">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C129">
-        <v>444</v>
+        <v>45</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -1810,7 +1810,7 @@
         <v>3</v>
       </c>
       <c r="C130">
-        <v>93</v>
+        <v>182</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -1826,321 +1826,200 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13109</v>
+        <v>13116</v>
       </c>
       <c r="B132">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C132">
-        <v>312</v>
+        <v>21</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13116</v>
+        <v>13269</v>
       </c>
       <c r="B133">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C133">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13244</v>
+        <v>13407</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C134">
-        <v>23</v>
+        <v>66</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13293</v>
+        <v>13962</v>
       </c>
       <c r="B135">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>356</v>
+        <v>45</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13407</v>
+        <v>19981</v>
       </c>
       <c r="B136">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C136">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13462</v>
+        <v>20556</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C137">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>19879</v>
+        <v>20650</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>19966</v>
+        <v>21686</v>
       </c>
       <c r="B139">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C139">
-        <v>44</v>
+        <v>492</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>19981</v>
+        <v>21773</v>
       </c>
       <c r="B140">
         <v>2</v>
       </c>
       <c r="C140">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>20555</v>
+        <v>21793</v>
       </c>
       <c r="B141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C141">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>20556</v>
+        <v>22573</v>
       </c>
       <c r="B142">
         <v>2</v>
       </c>
       <c r="C142">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>20650</v>
+        <v>23235</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C143">
-        <v>70</v>
+        <v>37</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>20927</v>
+        <v>23248</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C144">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>20953</v>
+        <v>23262</v>
       </c>
       <c r="B145">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C145">
-        <v>7</v>
+        <v>135</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>21704</v>
+        <v>24252</v>
       </c>
       <c r="B146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>685</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>21710</v>
+        <v>24253</v>
       </c>
       <c r="B147">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>269</v>
+        <v>88</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>21773</v>
+        <v>24257</v>
       </c>
       <c r="B148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C148">
-        <v>36</v>
+        <v>64</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>22316</v>
+        <v>24724</v>
       </c>
       <c r="B149">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C149">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150">
-        <v>22361</v>
-      </c>
-      <c r="B150">
-        <v>1</v>
-      </c>
-      <c r="C150">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151">
-        <v>22573</v>
-      </c>
-      <c r="B151">
-        <v>2</v>
-      </c>
-      <c r="C151">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152">
-        <v>23262</v>
-      </c>
-      <c r="B152">
-        <v>2</v>
-      </c>
-      <c r="C152">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153">
-        <v>23488</v>
-      </c>
-      <c r="B153">
-        <v>3</v>
-      </c>
-      <c r="C153">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154">
-        <v>24121</v>
-      </c>
-      <c r="B154">
-        <v>3</v>
-      </c>
-      <c r="C154">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155">
-        <v>24252</v>
-      </c>
-      <c r="B155">
-        <v>1</v>
-      </c>
-      <c r="C155">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156">
-        <v>24253</v>
-      </c>
-      <c r="B156">
-        <v>1</v>
-      </c>
-      <c r="C156">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="A157">
-        <v>24256</v>
-      </c>
-      <c r="B157">
-        <v>1</v>
-      </c>
-      <c r="C157">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="A158">
-        <v>24257</v>
-      </c>
-      <c r="B158">
-        <v>1</v>
-      </c>
-      <c r="C158">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159">
-        <v>24707</v>
-      </c>
-      <c r="B159">
-        <v>3</v>
-      </c>
-      <c r="C159">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160">
-        <v>24724</v>
-      </c>
-      <c r="B160">
-        <v>2</v>
-      </c>
-      <c r="C160">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,13 +396,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -418,153 +418,153 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>338</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>192</v>
+        <v>145</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>675</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>216</v>
+        <v>336</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>408</v>
+        <v>345</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8">
-        <v>301</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>417</v>
+        <v>361</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>475</v>
+        <v>362</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>21</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>523</v>
+        <v>378</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11">
-        <v>69</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>590</v>
+        <v>405</v>
       </c>
       <c r="B12">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>125</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>949</v>
+        <v>408</v>
       </c>
       <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
         <v>10</v>
-      </c>
-      <c r="C13">
-        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>1007</v>
+        <v>590</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>118</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>1012</v>
+        <v>949</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>1309</v>
+        <v>990</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>1598</v>
+        <v>1012</v>
       </c>
       <c r="B17">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -572,282 +572,282 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>1601</v>
+        <v>1126</v>
       </c>
       <c r="B18">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>77</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1602</v>
+        <v>1446</v>
       </c>
       <c r="B19">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>75</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1655</v>
+        <v>1598</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C20">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>1691</v>
+        <v>1601</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C21">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>2057</v>
+        <v>1602</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C22">
-        <v>213</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>2108</v>
+        <v>2049</v>
       </c>
       <c r="B23">
         <v>3</v>
       </c>
       <c r="C23">
-        <v>122</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>2161</v>
+        <v>2050</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24">
-        <v>54</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>2188</v>
+        <v>2054</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>2193</v>
+        <v>2055</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C26">
-        <v>51</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>2194</v>
+        <v>2057</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>50</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>2323</v>
+        <v>2161</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>55</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>2331</v>
+        <v>2193</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>2423</v>
+        <v>2194</v>
       </c>
       <c r="B30">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>112</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>2424</v>
+        <v>2323</v>
       </c>
       <c r="B31">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>78</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>2497</v>
+        <v>2423</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C32">
-        <v>77</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2505</v>
+        <v>2424</v>
       </c>
       <c r="B33">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2508</v>
+        <v>2504</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2774</v>
+        <v>2505</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C35">
-        <v>75</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2775</v>
+        <v>2506</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C36">
-        <v>61</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2778</v>
+        <v>2508</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37">
-        <v>81</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2803</v>
+        <v>2774</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38">
-        <v>111</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>3073</v>
+        <v>2803</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>3080</v>
+        <v>2912</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>70</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>3131</v>
+        <v>3071</v>
       </c>
       <c r="B41">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>149</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>3495</v>
+        <v>3073</v>
       </c>
       <c r="B42">
         <v>3</v>
       </c>
       <c r="C42">
-        <v>1190</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>3584</v>
+        <v>3080</v>
       </c>
       <c r="B43">
         <v>3</v>
@@ -858,73 +858,73 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>3670</v>
+        <v>3131</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>3892</v>
+        <v>3462</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>3898</v>
+        <v>3495</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>3906</v>
+        <v>3576</v>
       </c>
       <c r="B47">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3909</v>
+        <v>3577</v>
       </c>
       <c r="B48">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C48">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>4592</v>
+        <v>3581</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>4594</v>
+        <v>3584</v>
       </c>
       <c r="B50">
         <v>3</v>
@@ -935,73 +935,73 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>4672</v>
+        <v>3840</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
       <c r="C51">
-        <v>27</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>4867</v>
+        <v>3892</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>5111</v>
+        <v>3898</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>53</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>5152</v>
+        <v>3906</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C54">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>5208</v>
+        <v>3909</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C55">
-        <v>254</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>5209</v>
+        <v>4592</v>
       </c>
       <c r="B56">
         <v>3</v>
       </c>
       <c r="C56">
-        <v>266</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>5243</v>
+        <v>4594</v>
       </c>
       <c r="B57">
         <v>3</v>
@@ -1012,65 +1012,65 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5538</v>
+        <v>4672</v>
       </c>
       <c r="B58">
         <v>1</v>
       </c>
       <c r="C58">
-        <v>78</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5539</v>
+        <v>4867</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5541</v>
+        <v>5152</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5577</v>
+        <v>5165</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>99</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5585</v>
+        <v>5209</v>
       </c>
       <c r="B62">
         <v>3</v>
       </c>
       <c r="C62">
-        <v>121</v>
+        <v>254</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5660</v>
+        <v>5243</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63">
         <v>7</v>
@@ -1078,142 +1078,142 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>6158</v>
+        <v>5538</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>305</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>6292</v>
+        <v>5539</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65">
-        <v>76</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>6294</v>
+        <v>5541</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>6494</v>
+        <v>5577</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>6540</v>
+        <v>5585</v>
       </c>
       <c r="B68">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>37</v>
+        <v>121</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>6575</v>
+        <v>5660</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>403</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>6630</v>
+        <v>6097</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C70">
-        <v>47</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>6936</v>
+        <v>6098</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C71">
-        <v>160</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6946</v>
+        <v>6158</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>28</v>
+        <v>119</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>7004</v>
+        <v>6292</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73">
-        <v>36</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>7084</v>
+        <v>6294</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>7363</v>
+        <v>6575</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>127</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>7517</v>
+        <v>6630</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76">
         <v>7</v>
@@ -1221,134 +1221,134 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>7673</v>
+        <v>6936</v>
       </c>
       <c r="B77">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>7886</v>
+        <v>6946</v>
       </c>
       <c r="B78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>64</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8156</v>
+        <v>7084</v>
       </c>
       <c r="B79">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>40</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8217</v>
+        <v>7363</v>
       </c>
       <c r="B80">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>197</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8285</v>
+        <v>7517</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>227</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8677</v>
+        <v>7673</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C82">
-        <v>140</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8926</v>
+        <v>8217</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C83">
-        <v>70</v>
+        <v>202</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8927</v>
+        <v>8283</v>
       </c>
       <c r="B84">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>996</v>
+        <v>215</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8943</v>
+        <v>8286</v>
       </c>
       <c r="B85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>178</v>
+        <v>216</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8944</v>
+        <v>8926</v>
       </c>
       <c r="B86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>101</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>9070</v>
+        <v>9065</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>15</v>
+        <v>138</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>9122</v>
+        <v>9070</v>
       </c>
       <c r="B88">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>129</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1364,51 +1364,51 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9358</v>
+        <v>9507</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>71</v>
+        <v>242</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9396</v>
+        <v>10149</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C91">
-        <v>87</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9507</v>
+        <v>10161</v>
       </c>
       <c r="B92">
         <v>3</v>
       </c>
       <c r="C92">
-        <v>92</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>10149</v>
+        <v>10595</v>
       </c>
       <c r="B93">
         <v>3</v>
       </c>
       <c r="C93">
-        <v>428</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>10161</v>
+        <v>10596</v>
       </c>
       <c r="B94">
         <v>3</v>
@@ -1419,7 +1419,7 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10596</v>
+        <v>10598</v>
       </c>
       <c r="B95">
         <v>3</v>
@@ -1447,7 +1447,7 @@
         <v>1</v>
       </c>
       <c r="C97">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1458,7 +1458,7 @@
         <v>3</v>
       </c>
       <c r="C98">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1469,62 +1469,62 @@
         <v>2</v>
       </c>
       <c r="C99">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>11093</v>
+        <v>11150</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100">
-        <v>36</v>
+        <v>159</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11150</v>
+        <v>11216</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C101">
-        <v>160</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11216</v>
+        <v>11403</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11402</v>
+        <v>11421</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C103">
-        <v>49</v>
+        <v>77</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11403</v>
+        <v>11426</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C104">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -1540,18 +1540,18 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11737</v>
+        <v>11738</v>
       </c>
       <c r="B106">
         <v>2</v>
       </c>
       <c r="C106">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11738</v>
+        <v>11739</v>
       </c>
       <c r="B107">
         <v>2</v>
@@ -1562,172 +1562,172 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11739</v>
+        <v>11772</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11767</v>
+        <v>11895</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>92</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11844</v>
+        <v>11911</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>124</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11895</v>
+        <v>11944</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C111">
-        <v>32</v>
+        <v>284</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11911</v>
+        <v>11967</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11944</v>
+        <v>11973</v>
       </c>
       <c r="B113">
         <v>3</v>
       </c>
       <c r="C113">
-        <v>280</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11967</v>
+        <v>11974</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C114">
-        <v>99</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11973</v>
+        <v>12028</v>
       </c>
       <c r="B115">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>7</v>
+        <v>337</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11974</v>
+        <v>12128</v>
       </c>
       <c r="B116">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12128</v>
+        <v>12243</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C117">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12269</v>
+        <v>12250</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C118">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12270</v>
+        <v>12269</v>
       </c>
       <c r="B119">
         <v>2</v>
       </c>
       <c r="C119">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12304</v>
+        <v>12270</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C120">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12340</v>
+        <v>12304</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C121">
-        <v>78</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12489</v>
+        <v>12340</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12505</v>
+        <v>12489</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -1738,287 +1738,364 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12535</v>
+        <v>12505</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C124">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12539</v>
+        <v>12535</v>
       </c>
       <c r="B125">
         <v>2</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12595</v>
+        <v>12539</v>
       </c>
       <c r="B126">
         <v>2</v>
       </c>
       <c r="C126">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12791</v>
+        <v>12595</v>
       </c>
       <c r="B127">
         <v>2</v>
       </c>
       <c r="C127">
-        <v>376</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12904</v>
+        <v>12791</v>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C128">
-        <v>355</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12925</v>
+        <v>12904</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C129">
-        <v>45</v>
+        <v>149</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13030</v>
+        <v>12925</v>
       </c>
       <c r="B130">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>182</v>
+        <v>36</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13045</v>
+        <v>12979</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>291</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13116</v>
+        <v>12980</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C132">
-        <v>21</v>
+        <v>297</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13269</v>
+        <v>13030</v>
       </c>
       <c r="B133">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C133">
-        <v>34</v>
+        <v>182</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13407</v>
+        <v>13045</v>
       </c>
       <c r="B134">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>66</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13962</v>
+        <v>13109</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C135">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>19981</v>
+        <v>13116</v>
       </c>
       <c r="B136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>20556</v>
+        <v>13259</v>
       </c>
       <c r="B137">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C137">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>20650</v>
+        <v>13269</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C138">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21686</v>
+        <v>13407</v>
       </c>
       <c r="B139">
         <v>3</v>
       </c>
       <c r="C139">
-        <v>492</v>
+        <v>66</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21773</v>
+        <v>19879</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>21793</v>
+        <v>19981</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>22573</v>
+        <v>20556</v>
       </c>
       <c r="B142">
         <v>2</v>
       </c>
       <c r="C142">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>23235</v>
+        <v>20650</v>
       </c>
       <c r="B143">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C143">
-        <v>37</v>
+        <v>70</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>23248</v>
+        <v>20953</v>
       </c>
       <c r="B144">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C144">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>23262</v>
+        <v>21710</v>
       </c>
       <c r="B145">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C145">
-        <v>135</v>
+        <v>268</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>24252</v>
+        <v>21773</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>24253</v>
+        <v>21793</v>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>24257</v>
+        <v>21798</v>
       </c>
       <c r="B148">
         <v>1</v>
       </c>
       <c r="C148">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
+        <v>23248</v>
+      </c>
+      <c r="B149">
+        <v>25</v>
+      </c>
+      <c r="C149">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>23262</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>24116</v>
+      </c>
+      <c r="B151">
+        <v>1</v>
+      </c>
+      <c r="C151">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
+        <v>24121</v>
+      </c>
+      <c r="B152">
+        <v>3</v>
+      </c>
+      <c r="C152">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>24132</v>
+      </c>
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>24252</v>
+      </c>
+      <c r="B154">
+        <v>1</v>
+      </c>
+      <c r="C154">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155">
+        <v>24253</v>
+      </c>
+      <c r="B155">
+        <v>1</v>
+      </c>
+      <c r="C155">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156">
         <v>24724</v>
       </c>
-      <c r="B149">
-        <v>2</v>
-      </c>
-      <c r="C149">
+      <c r="B156">
+        <v>2</v>
+      </c>
+      <c r="C156">
         <v>7</v>
       </c>
     </row>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_702.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C156"/>
+  <dimension ref="A1:C155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,7 +402,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -418,123 +418,123 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>69</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>70</v>
+        <v>674</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>336</v>
+        <v>307</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C8">
-        <v>234</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>68</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>378</v>
+        <v>408</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>205</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>405</v>
+        <v>590</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>299</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>408</v>
+        <v>616</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>590</v>
+        <v>944</v>
       </c>
       <c r="B14">
         <v>15</v>
       </c>
       <c r="C14">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -550,46 +550,46 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>64</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>1012</v>
+        <v>996</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>1126</v>
+        <v>1012</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>102</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1446</v>
+        <v>1309</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -622,34 +622,34 @@
         <v>68</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>2049</v>
+        <v>1654</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>248</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>2050</v>
+        <v>1699</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24">
-        <v>210</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>2054</v>
+        <v>2050</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -666,18 +666,18 @@
         <v>3</v>
       </c>
       <c r="C26">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>2057</v>
+        <v>2109</v>
       </c>
       <c r="B27">
         <v>3</v>
       </c>
       <c r="C27">
-        <v>209</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -715,123 +715,123 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>2323</v>
+        <v>2234</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>55</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>2423</v>
+        <v>2287</v>
       </c>
       <c r="B32">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="C32">
-        <v>112</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2424</v>
+        <v>2308</v>
       </c>
       <c r="B33">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="C33">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2504</v>
+        <v>2323</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>257</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2505</v>
+        <v>2331</v>
       </c>
       <c r="B35">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2506</v>
+        <v>2504</v>
       </c>
       <c r="B36">
         <v>10</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>258</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2508</v>
+        <v>2505</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2774</v>
+        <v>2506</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C38">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2803</v>
+        <v>2508</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39">
-        <v>110</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2912</v>
+        <v>2803</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>22</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>3071</v>
+        <v>2912</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -864,70 +864,70 @@
         <v>10</v>
       </c>
       <c r="C44">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>3462</v>
+        <v>3451</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>3495</v>
+        <v>3462</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>1199</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>3576</v>
+        <v>3478</v>
       </c>
       <c r="B47">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3577</v>
+        <v>3495</v>
       </c>
       <c r="B48">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>40</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3581</v>
+        <v>3584</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3584</v>
+        <v>3892</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C50">
         <v>7</v>
@@ -935,29 +935,29 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3840</v>
+        <v>3906</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C51">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3892</v>
+        <v>3909</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3898</v>
+        <v>4592</v>
       </c>
       <c r="B53">
         <v>3</v>
@@ -968,10 +968,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3906</v>
+        <v>4594</v>
       </c>
       <c r="B54">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C54">
         <v>7</v>
@@ -979,216 +979,216 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3909</v>
+        <v>4672</v>
       </c>
       <c r="B55">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>4592</v>
+        <v>4867</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4594</v>
+        <v>5152</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4672</v>
+        <v>5165</v>
       </c>
       <c r="B58">
         <v>1</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4867</v>
+        <v>5243</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C59">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5152</v>
+        <v>5538</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>11</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5165</v>
+        <v>5539</v>
       </c>
       <c r="B61">
         <v>1</v>
       </c>
       <c r="C61">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5209</v>
+        <v>5541</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>254</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5243</v>
+        <v>5577</v>
       </c>
       <c r="B63">
         <v>3</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5538</v>
+        <v>5585</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C64">
-        <v>79</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5539</v>
+        <v>5660</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5541</v>
+        <v>6097</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C66">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5577</v>
+        <v>6098</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C67">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5585</v>
+        <v>6158</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5660</v>
+        <v>6292</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>76</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>6097</v>
+        <v>6294</v>
       </c>
       <c r="B70">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>6098</v>
+        <v>6497</v>
       </c>
       <c r="B71">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6158</v>
+        <v>6575</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>6292</v>
+        <v>6630</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>76</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>6294</v>
+        <v>6946</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -1199,106 +1199,106 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6575</v>
+        <v>7084</v>
       </c>
       <c r="B75">
         <v>3</v>
       </c>
       <c r="C75">
-        <v>127</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6630</v>
+        <v>7202</v>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6936</v>
+        <v>7363</v>
       </c>
       <c r="B77">
         <v>2</v>
       </c>
       <c r="C77">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6946</v>
+        <v>7457</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C78">
-        <v>7</v>
+        <v>101</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>7084</v>
+        <v>7517</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>113</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>7363</v>
+        <v>7673</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C80">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>7517</v>
+        <v>7886</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C81">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>7673</v>
+        <v>8217</v>
       </c>
       <c r="B82">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C82">
-        <v>15</v>
+        <v>201</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8217</v>
+        <v>8284</v>
       </c>
       <c r="B83">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>202</v>
+        <v>216</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8283</v>
+        <v>8286</v>
       </c>
       <c r="B84">
         <v>2</v>
@@ -1309,13 +1309,13 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8286</v>
+        <v>8688</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C85">
-        <v>216</v>
+        <v>167</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1331,18 +1331,18 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>9065</v>
+        <v>8939</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>138</v>
+        <v>189</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>9070</v>
+        <v>9357</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>9357</v>
+        <v>9380</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -1370,23 +1370,23 @@
         <v>3</v>
       </c>
       <c r="C90">
-        <v>242</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>10149</v>
+        <v>10161</v>
       </c>
       <c r="B91">
         <v>3</v>
       </c>
       <c r="C91">
-        <v>1122</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>10161</v>
+        <v>10596</v>
       </c>
       <c r="B92">
         <v>3</v>
@@ -1397,21 +1397,21 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>10595</v>
+        <v>10599</v>
       </c>
       <c r="B93">
         <v>3</v>
       </c>
       <c r="C93">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>10596</v>
+        <v>10616</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C94">
         <v>7</v>
@@ -1419,18 +1419,18 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10598</v>
+        <v>10716</v>
       </c>
       <c r="B95">
         <v>3</v>
       </c>
       <c r="C95">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>10599</v>
+        <v>10717</v>
       </c>
       <c r="B96">
         <v>3</v>
@@ -1441,263 +1441,263 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10616</v>
+        <v>10720</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10717</v>
+        <v>10721</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C98">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10993</v>
+        <v>11150</v>
       </c>
       <c r="B99">
         <v>2</v>
       </c>
       <c r="C99">
-        <v>24</v>
+        <v>158</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>11150</v>
+        <v>11216</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>159</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11216</v>
+        <v>11403</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11403</v>
+        <v>11492</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11421</v>
+        <v>11738</v>
       </c>
       <c r="B103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11426</v>
+        <v>11739</v>
       </c>
       <c r="B104">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C104">
-        <v>52</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11492</v>
+        <v>11772</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11738</v>
+        <v>11895</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11739</v>
+        <v>11911</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11772</v>
+        <v>11944</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C108">
-        <v>7</v>
+        <v>286</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11895</v>
+        <v>11962</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11911</v>
+        <v>11967</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11944</v>
+        <v>11973</v>
       </c>
       <c r="B111">
         <v>3</v>
       </c>
       <c r="C111">
-        <v>284</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11967</v>
+        <v>11974</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C112">
-        <v>62</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11973</v>
+        <v>12028</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>338</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11974</v>
+        <v>12128</v>
       </c>
       <c r="B114">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>12028</v>
+        <v>12269</v>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115">
-        <v>337</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12128</v>
+        <v>12270</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12243</v>
+        <v>12340</v>
       </c>
       <c r="B117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>45</v>
+        <v>82</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12250</v>
+        <v>12346</v>
       </c>
       <c r="B118">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>356</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12269</v>
+        <v>12352</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>701</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12270</v>
+        <v>12489</v>
       </c>
       <c r="B120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -1705,32 +1705,32 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12304</v>
+        <v>12505</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12340</v>
+        <v>12535</v>
       </c>
       <c r="B122">
         <v>2</v>
       </c>
       <c r="C122">
-        <v>81</v>
+        <v>25</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12489</v>
+        <v>12539</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123">
         <v>7</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12505</v>
+        <v>12595</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -1749,134 +1749,134 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12535</v>
+        <v>12764</v>
       </c>
       <c r="B125">
         <v>2</v>
       </c>
       <c r="C125">
-        <v>25</v>
+        <v>333</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12539</v>
+        <v>12791</v>
       </c>
       <c r="B126">
         <v>2</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12595</v>
+        <v>12904</v>
       </c>
       <c r="B127">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>150</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12791</v>
+        <v>12925</v>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>8</v>
+        <v>72</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12904</v>
+        <v>12979</v>
       </c>
       <c r="B129">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C129">
-        <v>149</v>
+        <v>289</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12925</v>
+        <v>12980</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C130">
-        <v>36</v>
+        <v>297</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>12979</v>
+        <v>13023</v>
       </c>
       <c r="B131">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>291</v>
+        <v>265</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>12980</v>
+        <v>13030</v>
       </c>
       <c r="B132">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>297</v>
+        <v>182</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13030</v>
+        <v>13045</v>
       </c>
       <c r="B133">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C133">
-        <v>182</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13045</v>
+        <v>13109</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C134">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13109</v>
+        <v>13116</v>
       </c>
       <c r="B135">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13116</v>
+        <v>13257</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C136">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -1887,7 +1887,7 @@
         <v>29</v>
       </c>
       <c r="C137">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -1903,79 +1903,79 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>13407</v>
+        <v>13270</v>
       </c>
       <c r="B139">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C139">
-        <v>66</v>
+        <v>47</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>19879</v>
+        <v>13273</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>19981</v>
+        <v>13407</v>
       </c>
       <c r="B141">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C141">
-        <v>29</v>
+        <v>67</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>20556</v>
+        <v>13962</v>
       </c>
       <c r="B142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>20650</v>
+        <v>13968</v>
       </c>
       <c r="B143">
         <v>1</v>
       </c>
       <c r="C143">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>20953</v>
+        <v>19981</v>
       </c>
       <c r="B144">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>21710</v>
+        <v>20556</v>
       </c>
       <c r="B145">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C145">
-        <v>268</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -1991,24 +1991,24 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>21793</v>
+        <v>22325</v>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>106</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>21798</v>
+        <v>23235</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C148">
-        <v>82</v>
+        <v>37</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2035,7 +2035,7 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>24116</v>
+        <v>24252</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2046,56 +2046,45 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>24121</v>
+        <v>24253</v>
       </c>
       <c r="B152">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C152">
-        <v>95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>24132</v>
+        <v>24724</v>
       </c>
       <c r="B153">
         <v>2</v>
       </c>
       <c r="C153">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>24252</v>
+        <v>25587</v>
       </c>
       <c r="B154">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C154">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>24253</v>
+        <v>25700</v>
       </c>
       <c r="B155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C155">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156">
-        <v>24724</v>
-      </c>
-      <c r="B156">
-        <v>2</v>
-      </c>
-      <c r="C156">
         <v>7</v>
       </c>
     </row>
